--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -947,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118361108</v>
+        <v>118361209</v>
       </c>
       <c r="B4" t="n">
-        <v>97752</v>
+        <v>97763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,26 +963,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500092</v>
+        <v>499969</v>
       </c>
       <c r="R4" t="n">
-        <v>7013956</v>
+        <v>7013912</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118361209</v>
+        <v>118361108</v>
       </c>
       <c r="B5" t="n">
-        <v>97763</v>
+        <v>97752</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499969</v>
+        <v>500092</v>
       </c>
       <c r="R5" t="n">
-        <v>7013912</v>
+        <v>7013956</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118361074</v>
+        <v>118361155</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>96964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,45 +1775,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500083</v>
+        <v>500092</v>
       </c>
       <c r="R10" t="n">
-        <v>7013946</v>
+        <v>7013956</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1850,7 +1863,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1870,27 +1883,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1908,10 +1901,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118361155</v>
+        <v>118361074</v>
       </c>
       <c r="B11" t="n">
-        <v>96964</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1920,58 +1913,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500092</v>
+        <v>500083</v>
       </c>
       <c r="R11" t="n">
-        <v>7013956</v>
+        <v>7013946</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2008,7 +1988,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2028,7 +2008,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -947,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118361209</v>
+        <v>118361108</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>97752</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,26 +963,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499969</v>
+        <v>500092</v>
       </c>
       <c r="R4" t="n">
-        <v>7013912</v>
+        <v>7013956</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118361108</v>
+        <v>118361209</v>
       </c>
       <c r="B5" t="n">
-        <v>97752</v>
+        <v>97763</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500092</v>
+        <v>499969</v>
       </c>
       <c r="R5" t="n">
-        <v>7013956</v>
+        <v>7013912</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118361155</v>
+        <v>118361074</v>
       </c>
       <c r="B10" t="n">
-        <v>96964</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,58 +1775,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500092</v>
+        <v>500083</v>
       </c>
       <c r="R10" t="n">
-        <v>7013956</v>
+        <v>7013946</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1863,7 +1850,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1883,7 +1870,27 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1901,10 +1908,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118361074</v>
+        <v>118361155</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>96964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1913,45 +1920,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500083</v>
+        <v>500092</v>
       </c>
       <c r="R11" t="n">
-        <v>7013946</v>
+        <v>7013956</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1988,7 +2008,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2008,27 +2028,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118361190</v>
+        <v>118361074</v>
       </c>
       <c r="B2" t="n">
-        <v>97750</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,58 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499996</v>
+        <v>500083</v>
       </c>
       <c r="R2" t="n">
-        <v>7013908</v>
+        <v>7013946</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +782,27 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -947,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118361108</v>
+        <v>118361209</v>
       </c>
       <c r="B4" t="n">
-        <v>97752</v>
+        <v>97763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,26 +970,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +999,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1007,10 +1014,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500092</v>
+        <v>499969</v>
       </c>
       <c r="R4" t="n">
-        <v>7013956</v>
+        <v>7013912</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,7 +1054,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,7 +1074,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1085,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118361209</v>
+        <v>118361171</v>
       </c>
       <c r="B5" t="n">
-        <v>97763</v>
+        <v>97752</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,26 +1108,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1130,7 +1137,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1145,10 +1152,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499969</v>
+        <v>500089</v>
       </c>
       <c r="R5" t="n">
-        <v>7013912</v>
+        <v>7013986</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1192,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,7 +1212,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1223,10 +1230,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118361186</v>
+        <v>118361047</v>
       </c>
       <c r="B6" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,53 +1242,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500087</v>
+        <v>500058</v>
       </c>
       <c r="R6" t="n">
-        <v>7013981</v>
+        <v>7013944</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1315,7 +1326,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,7 +1346,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1353,10 +1364,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118361047</v>
+        <v>118361186</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,57 +1376,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500058</v>
+        <v>500087</v>
       </c>
       <c r="R7" t="n">
-        <v>7013944</v>
+        <v>7013981</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1449,7 +1456,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,7 +1476,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1487,10 +1494,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118361183</v>
+        <v>118361011</v>
       </c>
       <c r="B8" t="n">
-        <v>96964</v>
+        <v>57443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1499,43 +1506,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222741</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1543,17 +1546,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500087</v>
+        <v>500047</v>
       </c>
       <c r="R8" t="n">
-        <v>7013981</v>
+        <v>7013959</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1587,7 +1590,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1596,7 +1599,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1609,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1625,7 +1627,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118361123</v>
+        <v>118361025</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1660,7 +1662,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1685,10 +1687,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500092</v>
+        <v>500048</v>
       </c>
       <c r="R9" t="n">
-        <v>7013956</v>
+        <v>7013963</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1725,7 +1727,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar och 3 st blomstänglar med knopp samt 1 st vinterståndare inom ca 2 m2 yta. Här finns även andra orkidéarter såsom guckusko, tvåblad och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,7 +1747,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1763,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118361074</v>
+        <v>118361155</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>96964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,45 +1777,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500083</v>
+        <v>500092</v>
       </c>
       <c r="R10" t="n">
-        <v>7013946</v>
+        <v>7013956</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1850,7 +1865,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1870,27 +1885,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1908,10 +1903,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118361155</v>
+        <v>118361154</v>
       </c>
       <c r="B11" t="n">
-        <v>96964</v>
+        <v>97763</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1924,26 +1919,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222741</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1953,7 +1948,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -2008,7 +2003,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2046,10 +2041,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118361182</v>
+        <v>118361123</v>
       </c>
       <c r="B12" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2058,30 +2053,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2091,7 +2086,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2106,10 +2101,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500089</v>
+        <v>500092</v>
       </c>
       <c r="R12" t="n">
-        <v>7013986</v>
+        <v>7013956</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2146,7 +2141,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar och 3 st blomstänglar med knopp samt 1 st vinterståndare inom ca 2 m2 yta. Här finns även andra orkidéarter såsom guckusko, tvåblad och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2184,10 +2179,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118361011</v>
+        <v>118361182</v>
       </c>
       <c r="B13" t="n">
-        <v>57443</v>
+        <v>97763</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2196,39 +2191,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2236,17 +2235,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500047</v>
+        <v>500089</v>
       </c>
       <c r="R13" t="n">
-        <v>7013959</v>
+        <v>7013986</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2280,7 +2279,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2289,6 +2288,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118361171</v>
+        <v>118361108</v>
       </c>
       <c r="B14" t="n">
         <v>97752</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500089</v>
+        <v>500092</v>
       </c>
       <c r="R14" t="n">
-        <v>7013986</v>
+        <v>7013956</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118361066</v>
+        <v>118361145</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2467,30 +2467,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500083</v>
+        <v>500092</v>
       </c>
       <c r="R15" t="n">
-        <v>7013946</v>
+        <v>7013956</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118361154</v>
+        <v>118361190</v>
       </c>
       <c r="B16" t="n">
-        <v>97763</v>
+        <v>97750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2609,21 +2609,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500092</v>
+        <v>499996</v>
       </c>
       <c r="R16" t="n">
-        <v>7013956</v>
+        <v>7013908</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118361145</v>
+        <v>118361066</v>
       </c>
       <c r="B17" t="n">
-        <v>97869</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2743,30 +2743,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500092</v>
+        <v>500083</v>
       </c>
       <c r="R17" t="n">
-        <v>7013956</v>
+        <v>7013946</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118361025</v>
+        <v>118361183</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>96964</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2881,30 +2881,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500048</v>
+        <v>500087</v>
       </c>
       <c r="R18" t="n">
-        <v>7013963</v>
+        <v>7013981</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -2317,10 +2317,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118361108</v>
+        <v>118361145</v>
       </c>
       <c r="B14" t="n">
-        <v>97752</v>
+        <v>97869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2333,26 +2333,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2455,10 +2455,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118361145</v>
+        <v>118361190</v>
       </c>
       <c r="B15" t="n">
-        <v>97869</v>
+        <v>97750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2471,26 +2471,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500092</v>
+        <v>499996</v>
       </c>
       <c r="R15" t="n">
-        <v>7013956</v>
+        <v>7013908</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118361190</v>
+        <v>118361108</v>
       </c>
       <c r="B16" t="n">
-        <v>97750</v>
+        <v>97752</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2609,26 +2609,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499996</v>
+        <v>500092</v>
       </c>
       <c r="R16" t="n">
-        <v>7013908</v>
+        <v>7013956</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118361074</v>
+        <v>118361186</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500083</v>
+        <v>500087</v>
       </c>
       <c r="R2" t="n">
-        <v>7013946</v>
+        <v>7013981</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,27 +787,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118361184</v>
+        <v>118361047</v>
       </c>
       <c r="B3" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,30 +817,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,7 +850,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -876,13 +861,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500087</v>
+        <v>500058</v>
       </c>
       <c r="R3" t="n">
-        <v>7013981</v>
+        <v>7013944</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 1 st skott/stjälk med blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,7 +921,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118361209</v>
+        <v>118361183</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>96964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,26 +955,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>222741</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1014,10 +999,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499969</v>
+        <v>500087</v>
       </c>
       <c r="R4" t="n">
-        <v>7013912</v>
+        <v>7013981</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1054,7 +1039,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,7 +1059,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118361171</v>
+        <v>118361145</v>
       </c>
       <c r="B5" t="n">
-        <v>97752</v>
+        <v>97869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,26 +1093,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1137,7 +1122,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1152,10 +1137,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500089</v>
+        <v>500092</v>
       </c>
       <c r="R5" t="n">
-        <v>7013986</v>
+        <v>7013956</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1192,7 +1177,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,7 +1197,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1230,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118361047</v>
+        <v>118361209</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,30 +1227,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,24 +1260,28 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500058</v>
+        <v>499969</v>
       </c>
       <c r="R6" t="n">
-        <v>7013944</v>
+        <v>7013912</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1326,7 +1315,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,7 +1335,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1364,10 +1353,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118361186</v>
+        <v>118361123</v>
       </c>
       <c r="B7" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,32 +1365,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1416,10 +1413,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500087</v>
+        <v>500092</v>
       </c>
       <c r="R7" t="n">
-        <v>7013981</v>
+        <v>7013956</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1456,7 +1453,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar och 3 st blomstänglar med knopp samt 1 st vinterståndare inom ca 2 m2 yta. Här finns även andra orkidéarter såsom guckusko, tvåblad och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1476,7 +1473,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1494,10 +1491,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118361011</v>
+        <v>118361066</v>
       </c>
       <c r="B8" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1506,39 +1503,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1546,17 +1547,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500047</v>
+        <v>500083</v>
       </c>
       <c r="R8" t="n">
-        <v>7013959</v>
+        <v>7013946</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1590,7 +1591,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,6 +1600,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1609,7 +1611,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1765,10 +1767,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118361155</v>
+        <v>118361184</v>
       </c>
       <c r="B10" t="n">
-        <v>96964</v>
+        <v>97867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1781,26 +1783,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1810,25 +1812,21 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500092</v>
+        <v>500087</v>
       </c>
       <c r="R10" t="n">
-        <v>7013956</v>
+        <v>7013981</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1865,7 +1863,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 1 st skott/stjälk med blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1885,7 +1883,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1903,10 +1901,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118361154</v>
+        <v>118361074</v>
       </c>
       <c r="B11" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1915,58 +1913,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500092</v>
+        <v>500083</v>
       </c>
       <c r="R11" t="n">
-        <v>7013956</v>
+        <v>7013946</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2003,7 +1988,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2023,7 +2008,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118361123</v>
+        <v>118361155</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>96964</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2053,30 +2058,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2086,7 +2091,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2141,7 +2146,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar och 3 st blomstänglar med knopp samt 1 st vinterståndare inom ca 2 m2 yta. Här finns även andra orkidéarter såsom guckusko, tvåblad och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2179,10 +2184,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118361182</v>
+        <v>118361108</v>
       </c>
       <c r="B13" t="n">
-        <v>97763</v>
+        <v>97752</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2195,26 +2200,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2224,7 +2229,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2239,10 +2244,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500089</v>
+        <v>500092</v>
       </c>
       <c r="R13" t="n">
-        <v>7013986</v>
+        <v>7013956</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2279,7 +2284,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2299,7 +2304,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2317,10 +2322,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118361145</v>
+        <v>118361171</v>
       </c>
       <c r="B14" t="n">
-        <v>97869</v>
+        <v>97752</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2333,26 +2338,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2362,7 +2367,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2377,10 +2382,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500092</v>
+        <v>500089</v>
       </c>
       <c r="R14" t="n">
-        <v>7013956</v>
+        <v>7013986</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2417,7 +2422,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2437,7 +2442,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2455,10 +2460,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118361190</v>
+        <v>118361182</v>
       </c>
       <c r="B15" t="n">
-        <v>97750</v>
+        <v>97763</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2471,26 +2476,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2500,7 +2505,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499996</v>
+        <v>500089</v>
       </c>
       <c r="R15" t="n">
-        <v>7013908</v>
+        <v>7013986</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2555,7 +2560,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2575,7 +2580,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2593,10 +2598,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118361108</v>
+        <v>118361154</v>
       </c>
       <c r="B16" t="n">
-        <v>97752</v>
+        <v>97763</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2609,26 +2614,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2638,7 +2643,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2693,7 +2698,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2731,10 +2736,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118361066</v>
+        <v>118361011</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2743,43 +2748,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2787,17 +2788,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500083</v>
+        <v>500047</v>
       </c>
       <c r="R17" t="n">
-        <v>7013946</v>
+        <v>7013959</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2831,7 +2832,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2840,7 +2841,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118361183</v>
+        <v>118361190</v>
       </c>
       <c r="B18" t="n">
-        <v>96964</v>
+        <v>97750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2885,26 +2885,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222741</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500087</v>
+        <v>499996</v>
       </c>
       <c r="R18" t="n">
-        <v>7013981</v>
+        <v>7013908</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118361186</v>
+        <v>118361209</v>
       </c>
       <c r="B2" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,8 +708,16 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -727,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500087</v>
+        <v>499969</v>
       </c>
       <c r="R2" t="n">
-        <v>7013981</v>
+        <v>7013912</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +795,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118361047</v>
+        <v>118361186</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,57 +825,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500058</v>
+        <v>500087</v>
       </c>
       <c r="R3" t="n">
-        <v>7013944</v>
+        <v>7013981</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +925,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118361183</v>
+        <v>118361154</v>
       </c>
       <c r="B4" t="n">
-        <v>96964</v>
+        <v>97770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,26 +959,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222741</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -999,10 +1003,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500087</v>
+        <v>500092</v>
       </c>
       <c r="R4" t="n">
-        <v>7013981</v>
+        <v>7013956</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1039,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1063,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118361145</v>
+        <v>118361183</v>
       </c>
       <c r="B5" t="n">
-        <v>97869</v>
+        <v>96971</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,26 +1097,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>222741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1122,7 +1126,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1137,10 +1141,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500092</v>
+        <v>500087</v>
       </c>
       <c r="R5" t="n">
-        <v>7013956</v>
+        <v>7013981</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1177,7 +1181,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,7 +1201,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1215,10 +1219,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118361209</v>
+        <v>118361066</v>
       </c>
       <c r="B6" t="n">
-        <v>97763</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,30 +1231,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499969</v>
+        <v>500083</v>
       </c>
       <c r="R6" t="n">
-        <v>7013912</v>
+        <v>7013946</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1315,7 +1319,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1356,7 +1360,7 @@
         <v>118361123</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1491,10 +1495,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118361066</v>
+        <v>118361145</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1503,30 +1507,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1536,7 +1540,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1551,10 +1555,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500083</v>
+        <v>500092</v>
       </c>
       <c r="R8" t="n">
-        <v>7013946</v>
+        <v>7013956</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1591,7 +1595,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,7 +1615,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1629,10 +1633,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118361025</v>
+        <v>118361184</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1641,30 +1645,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1674,25 +1678,21 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500048</v>
+        <v>500087</v>
       </c>
       <c r="R9" t="n">
-        <v>7013963</v>
+        <v>7013981</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 1 st skott/stjälk med blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118361184</v>
+        <v>118361011</v>
       </c>
       <c r="B10" t="n">
-        <v>97867</v>
+        <v>57443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1779,25 +1779,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1805,31 +1805,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500087</v>
+        <v>500047</v>
       </c>
       <c r="R10" t="n">
-        <v>7013981</v>
+        <v>7013959</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 1 st skott/stjälk med blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1872,7 +1872,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1883,7 +1882,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1904,7 +1903,7 @@
         <v>118361074</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2046,10 +2045,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118361155</v>
+        <v>118361025</v>
       </c>
       <c r="B12" t="n">
-        <v>96964</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2058,30 +2057,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2091,7 +2090,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2106,10 +2105,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500092</v>
+        <v>500048</v>
       </c>
       <c r="R12" t="n">
-        <v>7013956</v>
+        <v>7013963</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2146,7 +2145,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,7 +2165,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2184,10 +2183,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118361108</v>
+        <v>118361182</v>
       </c>
       <c r="B13" t="n">
-        <v>97752</v>
+        <v>97770</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2200,26 +2199,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2229,7 +2228,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2244,10 +2243,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500092</v>
+        <v>500089</v>
       </c>
       <c r="R13" t="n">
-        <v>7013956</v>
+        <v>7013986</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2284,7 +2283,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2304,7 +2303,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2325,7 +2324,7 @@
         <v>118361171</v>
       </c>
       <c r="B14" t="n">
-        <v>97752</v>
+        <v>97759</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2460,10 +2459,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118361182</v>
+        <v>118361190</v>
       </c>
       <c r="B15" t="n">
-        <v>97763</v>
+        <v>97757</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2476,26 +2475,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2505,7 +2504,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500089</v>
+        <v>499996</v>
       </c>
       <c r="R15" t="n">
-        <v>7013986</v>
+        <v>7013908</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2560,7 +2559,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2580,7 +2579,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2598,10 +2597,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118361154</v>
+        <v>118361108</v>
       </c>
       <c r="B16" t="n">
-        <v>97763</v>
+        <v>97759</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2614,26 +2613,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2643,7 +2642,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2698,7 +2697,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2736,10 +2735,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118361011</v>
+        <v>118361047</v>
       </c>
       <c r="B17" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2748,54 +2747,54 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500047</v>
+        <v>500058</v>
       </c>
       <c r="R17" t="n">
-        <v>7013959</v>
+        <v>7013944</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2832,7 +2831,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2841,6 +2840,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118361190</v>
+        <v>118361155</v>
       </c>
       <c r="B18" t="n">
-        <v>97750</v>
+        <v>96971</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2885,26 +2885,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>222741</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499996</v>
+        <v>500092</v>
       </c>
       <c r="R18" t="n">
-        <v>7013908</v>
+        <v>7013956</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118361025</v>
+        <v>118361182</v>
       </c>
       <c r="B12" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2057,30 +2057,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500048</v>
+        <v>500089</v>
       </c>
       <c r="R12" t="n">
-        <v>7013963</v>
+        <v>7013986</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118361182</v>
+        <v>118361025</v>
       </c>
       <c r="B13" t="n">
-        <v>97770</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2195,30 +2195,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500089</v>
+        <v>500048</v>
       </c>
       <c r="R13" t="n">
-        <v>7013986</v>
+        <v>7013963</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118361171</v>
+        <v>118361190</v>
       </c>
       <c r="B14" t="n">
-        <v>97759</v>
+        <v>97757</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2337,26 +2337,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500089</v>
+        <v>499996</v>
       </c>
       <c r="R14" t="n">
-        <v>7013986</v>
+        <v>7013908</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118361190</v>
+        <v>118361171</v>
       </c>
       <c r="B15" t="n">
-        <v>97757</v>
+        <v>97759</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2475,26 +2475,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>504</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499996</v>
+        <v>500089</v>
       </c>
       <c r="R15" t="n">
-        <v>7013908</v>
+        <v>7013986</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118361209</v>
+        <v>118361171</v>
       </c>
       <c r="B2" t="n">
-        <v>97770</v>
+        <v>97759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499969</v>
+        <v>500089</v>
       </c>
       <c r="R2" t="n">
-        <v>7013912</v>
+        <v>7013986</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +795,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,7 +813,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118361186</v>
+        <v>118361209</v>
       </c>
       <c r="B3" t="n">
         <v>97770</v>
@@ -846,8 +846,16 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -865,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500087</v>
+        <v>499969</v>
       </c>
       <c r="R3" t="n">
-        <v>7013981</v>
+        <v>7013912</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,7 +913,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 7 st skott/stjälkar med blomstänglar vid ett gammalt dike med svagt rinnande vatten. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +933,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118361154</v>
+        <v>118361047</v>
       </c>
       <c r="B4" t="n">
-        <v>97770</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,30 +963,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -988,28 +996,24 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500092</v>
+        <v>500058</v>
       </c>
       <c r="R4" t="n">
-        <v>7013956</v>
+        <v>7013944</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1047,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,7 +1067,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,10 +1085,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118361183</v>
+        <v>118361123</v>
       </c>
       <c r="B5" t="n">
-        <v>96971</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,30 +1097,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1126,7 +1130,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1141,10 +1145,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500087</v>
+        <v>500092</v>
       </c>
       <c r="R5" t="n">
-        <v>7013981</v>
+        <v>7013956</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1181,7 +1185,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar och 3 st blomstänglar med knopp samt 1 st vinterståndare inom ca 2 m2 yta. Här finns även andra orkidéarter såsom guckusko, tvåblad och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1201,7 +1205,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1219,10 +1223,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118361066</v>
+        <v>118361155</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>96971</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1231,30 +1235,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1279,10 +1283,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500083</v>
+        <v>500092</v>
       </c>
       <c r="R6" t="n">
-        <v>7013946</v>
+        <v>7013956</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1319,7 +1323,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1339,7 +1343,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1357,10 +1361,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118361123</v>
+        <v>118361145</v>
       </c>
       <c r="B7" t="n">
-        <v>97853</v>
+        <v>97876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,30 +1373,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1402,7 +1406,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1457,7 +1461,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar och 3 st blomstänglar med knopp samt 1 st vinterståndare inom ca 2 m2 yta. Här finns även andra orkidéarter såsom guckusko, tvåblad och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1495,10 +1499,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118361145</v>
+        <v>118361154</v>
       </c>
       <c r="B8" t="n">
-        <v>97876</v>
+        <v>97770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1511,26 +1515,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1595,7 +1599,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Tvåblad med minst 8 st skott/stjälkar och 5 st blomstänglar i blom inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 2 st blomstänglar inom ca 6 m2 yta. Här finns även andra orkidéarter såsom guckusko, knärot och tvåblad. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1633,10 +1637,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118361184</v>
+        <v>118361186</v>
       </c>
       <c r="B9" t="n">
-        <v>97874</v>
+        <v>97770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1649,40 +1653,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 1 st skott/stjälk med blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med flera blomstänglar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1767,10 +1767,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118361011</v>
+        <v>118361190</v>
       </c>
       <c r="B10" t="n">
-        <v>57443</v>
+        <v>97757</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1779,39 +1779,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1819,17 +1823,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500047</v>
+        <v>499996</v>
       </c>
       <c r="R10" t="n">
-        <v>7013959</v>
+        <v>7013908</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1863,7 +1867,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1872,6 +1876,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1882,7 +1887,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1900,10 +1905,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118361074</v>
+        <v>118361184</v>
       </c>
       <c r="B11" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1912,34 +1917,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1947,10 +1961,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500083</v>
+        <v>500087</v>
       </c>
       <c r="R11" t="n">
-        <v>7013946</v>
+        <v>7013981</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1987,7 +2001,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 1 st skott/stjälk med blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2007,27 +2021,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2045,10 +2039,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118361182</v>
+        <v>118361011</v>
       </c>
       <c r="B12" t="n">
-        <v>97770</v>
+        <v>57443</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2057,43 +2051,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2101,17 +2091,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500089</v>
+        <v>500047</v>
       </c>
       <c r="R12" t="n">
-        <v>7013986</v>
+        <v>7013959</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2145,7 +2135,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Observerad i äldre skyddsvärd granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2154,7 +2144,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2165,7 +2154,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2183,10 +2172,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118361025</v>
+        <v>118361074</v>
       </c>
       <c r="B13" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2195,58 +2184,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500048</v>
+        <v>500083</v>
       </c>
       <c r="R13" t="n">
-        <v>7013963</v>
+        <v>7013946</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2283,7 +2259,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxta bålar av garnlav på gran där vissa bålar är fertila med apothecier. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2304,6 +2280,26 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2321,10 +2317,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118361190</v>
+        <v>118361183</v>
       </c>
       <c r="B14" t="n">
-        <v>97757</v>
+        <v>96971</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2337,26 +2333,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>222741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2366,7 +2362,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2381,10 +2377,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499996</v>
+        <v>500087</v>
       </c>
       <c r="R14" t="n">
-        <v>7013908</v>
+        <v>7013981</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2421,7 +2417,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Två stjälkar med överblommad korallrot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Finbräken med minst 32 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2441,7 +2437,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog på frisk-fuktig och fuktig mark.</t>
+          <t>Kanten av en lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2459,10 +2455,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118361171</v>
+        <v>118361066</v>
       </c>
       <c r="B15" t="n">
-        <v>97759</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2471,30 +2467,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2504,7 +2500,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2519,10 +2515,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500089</v>
+        <v>500083</v>
       </c>
       <c r="R15" t="n">
-        <v>7013986</v>
+        <v>7013946</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2559,7 +2555,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Guckusko med minst 148 st skott/stjälkar och 37 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även fläcknycklar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 85 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2579,7 +2575,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2597,10 +2593,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118361108</v>
+        <v>118361025</v>
       </c>
       <c r="B16" t="n">
-        <v>97759</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2609,30 +2605,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2642,7 +2638,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2657,10 +2653,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500092</v>
+        <v>500048</v>
       </c>
       <c r="R16" t="n">
-        <v>7013956</v>
+        <v>7013963</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2697,7 +2693,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med 12 st skott/stjälkar och 2 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2717,7 +2713,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2735,10 +2731,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118361047</v>
+        <v>118361108</v>
       </c>
       <c r="B17" t="n">
-        <v>97853</v>
+        <v>97759</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2747,30 +2743,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2780,24 +2776,28 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500058</v>
+        <v>500092</v>
       </c>
       <c r="R17" t="n">
-        <v>7013944</v>
+        <v>7013956</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Knärot med 30 st skott/stjälkar och 4 st blomstänglar med knoppar. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Guckusko med minst 21 st skott/stjälkar och 7 st överblommade blomstänglar inom ca 2 m2 yta. Här finns även andra orkidéarter såsom tvåblad, fläcknycklar och knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118361155</v>
+        <v>118361182</v>
       </c>
       <c r="B18" t="n">
-        <v>96971</v>
+        <v>97770</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2885,26 +2885,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222741</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500092</v>
+        <v>500089</v>
       </c>
       <c r="R18" t="n">
-        <v>7013956</v>
+        <v>7013986</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Finbräken med minst 60 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 22 st skott/stjälkar med blomstänglar inom ett ca 15 meter långt fuktstråk. Här finns även guckusko. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>En luckig yta på mer frisk-fuktig mark med högörter och graminider i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka med ett ca 15 meter långt fuktstråk med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -15265,10 +15265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119457046</v>
+        <v>119458949</v>
       </c>
       <c r="B108" t="n">
-        <v>97907</v>
+        <v>97928</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -15277,40 +15277,32 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -15325,10 +15317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>500048</v>
+        <v>500062</v>
       </c>
       <c r="R108" t="n">
-        <v>7013860</v>
+        <v>7013856</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -15365,7 +15357,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster som här förekommer relativt allmänt i skogsbeståndet. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -15403,10 +15395,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119458949</v>
+        <v>119457046</v>
       </c>
       <c r="B109" t="n">
-        <v>97928</v>
+        <v>97907</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -15415,32 +15407,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -15455,10 +15455,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>500062</v>
+        <v>500048</v>
       </c>
       <c r="R109" t="n">
-        <v>7013856</v>
+        <v>7013860</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Spindelblomster som här förekommer relativt allmänt i skogsbeståndet. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -16083,10 +16083,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119547149</v>
+        <v>119546050</v>
       </c>
       <c r="B114" t="n">
-        <v>79635</v>
+        <v>97824</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -16099,40 +16099,57 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6461</v>
+        <v>219790</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500053</v>
+        <v>500098</v>
       </c>
       <c r="R114" t="n">
-        <v>7014032</v>
+        <v>7014055</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -16162,6 +16179,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Fläcknycklar med minst 2 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -16181,7 +16203,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -16199,10 +16221,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119546264</v>
+        <v>119547149</v>
       </c>
       <c r="B115" t="n">
-        <v>97928</v>
+        <v>79635</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -16215,49 +16237,40 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500096</v>
+        <v>500053</v>
       </c>
       <c r="R115" t="n">
-        <v>7014027</v>
+        <v>7014032</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -16287,11 +16300,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Spindelblomster finns relativt allmänt i skogsbeståndet här. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -16311,7 +16319,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -16329,10 +16337,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119546050</v>
+        <v>119546264</v>
       </c>
       <c r="B116" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -16345,36 +16353,28 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -16389,10 +16389,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500098</v>
+        <v>500096</v>
       </c>
       <c r="R116" t="n">
-        <v>7014055</v>
+        <v>7014027</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 2 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster finns relativt allmänt i skogsbeståndet här. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -17011,10 +17011,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119547394</v>
+        <v>119546219</v>
       </c>
       <c r="B121" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -17023,61 +17023,44 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500054</v>
+        <v>500096</v>
       </c>
       <c r="R121" t="n">
-        <v>7013984</v>
+        <v>7014027</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -17111,7 +17094,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Knärot med minst 82 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -17131,7 +17114,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -17149,7 +17132,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119545934</v>
+        <v>119547394</v>
       </c>
       <c r="B122" t="n">
         <v>97907</v>
@@ -17184,7 +17167,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -17209,13 +17192,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500098</v>
+        <v>500054</v>
       </c>
       <c r="R122" t="n">
-        <v>7014055</v>
+        <v>7013984</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -17249,7 +17232,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Knärot med minst 31 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 82 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -17269,7 +17252,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -17287,10 +17270,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119546219</v>
+        <v>119545934</v>
       </c>
       <c r="B123" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -17299,41 +17282,58 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500096</v>
+        <v>500098</v>
       </c>
       <c r="R123" t="n">
-        <v>7014027</v>
+        <v>7014055</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 31 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -17684,10 +17684,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119550025</v>
+        <v>119546892</v>
       </c>
       <c r="B126" t="n">
-        <v>97928</v>
+        <v>97824</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -17700,21 +17700,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -17729,7 +17729,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -17744,13 +17744,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500118</v>
+        <v>500110</v>
       </c>
       <c r="R126" t="n">
-        <v>7013961</v>
+        <v>7014062</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 4 st skott/stjälkar med överblommade blomstänglar inom ca 2 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -17822,10 +17822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119546892</v>
+        <v>119550025</v>
       </c>
       <c r="B127" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -17838,21 +17838,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -17882,13 +17882,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500110</v>
+        <v>500118</v>
       </c>
       <c r="R127" t="n">
-        <v>7014062</v>
+        <v>7013961</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 4 st skott/stjälkar med överblommade blomstänglar inom ca 2 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -15812,10 +15812,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119513253</v>
+        <v>119513974</v>
       </c>
       <c r="B112" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15824,50 +15824,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>500232</v>
+        <v>500223</v>
       </c>
       <c r="R112" t="n">
-        <v>7014119</v>
+        <v>7014125</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15904,7 +15895,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Här observerades både stjälkar/skott och överblommade blomstänglar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15925,6 +15916,26 @@
       <c r="AI112" t="inlineStr">
         <is>
           <t>Barrdominerad öppen och gles skog på fuktig och blöt mark. Klassas som sumpskog enligt Skogsstyrelsen.</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -15942,10 +15953,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119513974</v>
+        <v>119513253</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15954,41 +15965,50 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>500223</v>
+        <v>500232</v>
       </c>
       <c r="R113" t="n">
-        <v>7014125</v>
+        <v>7014119</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -16025,7 +16045,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Här observerades både stjälkar/skott och överblommade blomstänglar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -16046,26 +16066,6 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>Barrdominerad öppen och gles skog på fuktig och blöt mark. Klassas som sumpskog enligt Skogsstyrelsen.</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -16083,7 +16083,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119546050</v>
+        <v>119546175</v>
       </c>
       <c r="B114" t="n">
         <v>97824</v>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -16143,10 +16143,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500098</v>
+        <v>500096</v>
       </c>
       <c r="R114" t="n">
-        <v>7014055</v>
+        <v>7014027</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 2 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 1 st skott/stjälk med överblommad blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -16221,10 +16221,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119547149</v>
+        <v>119547116</v>
       </c>
       <c r="B115" t="n">
-        <v>79635</v>
+        <v>97928</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -16237,27 +16237,44 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
@@ -16300,6 +16317,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Spindelblomster med minst 21 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -16337,10 +16359,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119546264</v>
+        <v>119546892</v>
       </c>
       <c r="B116" t="n">
-        <v>97928</v>
+        <v>97824</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -16353,28 +16375,36 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -16389,13 +16419,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500096</v>
+        <v>500110</v>
       </c>
       <c r="R116" t="n">
-        <v>7014027</v>
+        <v>7014062</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -16429,7 +16459,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Spindelblomster finns relativt allmänt i skogsbeståndet här. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 4 st skott/stjälkar med överblommade blomstänglar inom ca 2 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -16449,7 +16479,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -16467,7 +16497,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119552989</v>
+        <v>119546089</v>
       </c>
       <c r="B117" t="n">
         <v>97928</v>
@@ -16500,8 +16530,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
           <t>gulnande löv/blad</t>
@@ -16519,10 +16557,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>499965</v>
+        <v>500098</v>
       </c>
       <c r="R117" t="n">
-        <v>7013893</v>
+        <v>7014055</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -16549,17 +16587,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Spindelblomster finns allmänt i skogsbeståndet där fyndplatsen ligger. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 3 st skott av spindelblomster inom ca 1 m2 yta. Arten finns relativt allmänt i skogsbeståndet här. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -16579,7 +16617,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd. På frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris.</t>
+          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -16597,7 +16635,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119547116</v>
+        <v>119546264</v>
       </c>
       <c r="B118" t="n">
         <v>97928</v>
@@ -16630,19 +16668,11 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -16657,13 +16687,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>500053</v>
+        <v>500096</v>
       </c>
       <c r="R118" t="n">
-        <v>7014032</v>
+        <v>7014027</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -16697,7 +16727,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 21 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster finns relativt allmänt i skogsbeståndet här. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16717,7 +16747,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -16735,7 +16765,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119547206</v>
+        <v>119552989</v>
       </c>
       <c r="B119" t="n">
         <v>97928</v>
@@ -16768,16 +16798,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>gulnande löv/blad</t>
@@ -16795,13 +16817,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500058</v>
+        <v>499965</v>
       </c>
       <c r="R119" t="n">
-        <v>7014017</v>
+        <v>7013893</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -16825,17 +16847,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster finns allmänt i skogsbeståndet där fyndplatsen ligger. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16855,7 +16877,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd. På frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16873,10 +16895,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119546676</v>
+        <v>119546219</v>
       </c>
       <c r="B120" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16885,61 +16907,44 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500110</v>
+        <v>500096</v>
       </c>
       <c r="R120" t="n">
-        <v>7014062</v>
+        <v>7014027</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -16973,7 +16978,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Knärot med minst 70 st skott/stjälkar och 2 st överblommade blomstänglar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16993,7 +16998,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -17011,10 +17016,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119546219</v>
+        <v>119547394</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -17023,44 +17028,61 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500096</v>
+        <v>500054</v>
       </c>
       <c r="R121" t="n">
-        <v>7014027</v>
+        <v>7013984</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -17094,7 +17116,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 82 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -17114,7 +17136,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -17132,10 +17154,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119547394</v>
+        <v>119550025</v>
       </c>
       <c r="B122" t="n">
-        <v>97907</v>
+        <v>97928</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -17144,30 +17166,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -17177,7 +17199,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -17192,13 +17214,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500054</v>
+        <v>500118</v>
       </c>
       <c r="R122" t="n">
-        <v>7013984</v>
+        <v>7013961</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -17232,7 +17254,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Knärot med minst 82 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -17252,7 +17274,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -17270,7 +17292,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119545934</v>
+        <v>119546676</v>
       </c>
       <c r="B123" t="n">
         <v>97907</v>
@@ -17305,7 +17327,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -17330,13 +17352,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>500098</v>
+        <v>500110</v>
       </c>
       <c r="R123" t="n">
-        <v>7014055</v>
+        <v>7014062</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -17370,7 +17392,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Knärot med minst 31 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 70 st skott/stjälkar och 2 st överblommade blomstänglar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -17390,7 +17412,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -17408,10 +17430,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119546089</v>
+        <v>119547149</v>
       </c>
       <c r="B124" t="n">
-        <v>97928</v>
+        <v>79635</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -17424,57 +17446,40 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500098</v>
+        <v>500053</v>
       </c>
       <c r="R124" t="n">
-        <v>7014055</v>
+        <v>7014032</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -17504,11 +17509,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Minst 3 st skott av spindelblomster inom ca 1 m2 yta. Arten finns relativt allmänt i skogsbeståndet här. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119546892</v>
+        <v>119547206</v>
       </c>
       <c r="B126" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -17700,21 +17700,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -17729,7 +17729,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -17744,10 +17744,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500110</v>
+        <v>500058</v>
       </c>
       <c r="R126" t="n">
-        <v>7014062</v>
+        <v>7014017</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 4 st skott/stjälkar med överblommade blomstänglar inom ca 2 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -17822,10 +17822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119550025</v>
+        <v>119545934</v>
       </c>
       <c r="B127" t="n">
-        <v>97928</v>
+        <v>97907</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -17834,30 +17834,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -17882,10 +17882,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>500118</v>
+        <v>500098</v>
       </c>
       <c r="R127" t="n">
-        <v>7013961</v>
+        <v>7014055</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 31 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -17960,7 +17960,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119546175</v>
+        <v>119546050</v>
       </c>
       <c r="B128" t="n">
         <v>97824</v>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -18005,7 +18005,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -18020,10 +18020,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500096</v>
+        <v>500098</v>
       </c>
       <c r="R128" t="n">
-        <v>7014027</v>
+        <v>7014055</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 1 st skott/stjälk med överblommad blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 2 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -16765,10 +16765,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119552989</v>
+        <v>119546219</v>
       </c>
       <c r="B119" t="n">
-        <v>97928</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16777,50 +16777,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>499965</v>
+        <v>500096</v>
       </c>
       <c r="R119" t="n">
-        <v>7013893</v>
+        <v>7014027</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -16847,17 +16838,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Spindelblomster finns allmänt i skogsbeståndet där fyndplatsen ligger. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16877,7 +16868,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd. På frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16895,10 +16886,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119546219</v>
+        <v>119552989</v>
       </c>
       <c r="B120" t="n">
-        <v>78526</v>
+        <v>97928</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -16907,41 +16898,50 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>500096</v>
+        <v>499965</v>
       </c>
       <c r="R120" t="n">
-        <v>7014027</v>
+        <v>7013893</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16968,17 +16968,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster finns allmänt i skogsbeståndet där fyndplatsen ligger. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd. På frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -17430,10 +17430,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119547149</v>
+        <v>119547929</v>
       </c>
       <c r="B124" t="n">
-        <v>79635</v>
+        <v>96862</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -17446,40 +17446,57 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500053</v>
+        <v>500035</v>
       </c>
       <c r="R124" t="n">
-        <v>7014032</v>
+        <v>7013945</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -17509,6 +17526,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Särskilt riklig utbredning av revlummer som här dominerar i stor del av fältskiktet inom minst 40 m2.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -17528,7 +17550,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -17546,10 +17568,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119547929</v>
+        <v>119547206</v>
       </c>
       <c r="B125" t="n">
-        <v>96862</v>
+        <v>97928</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -17562,36 +17584,36 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -17606,13 +17628,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500035</v>
+        <v>500058</v>
       </c>
       <c r="R125" t="n">
-        <v>7013945</v>
+        <v>7014017</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -17646,7 +17668,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Särskilt riklig utbredning av revlummer som här dominerar i stor del av fältskiktet inom minst 40 m2.</t>
+          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -17666,7 +17688,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -17684,10 +17706,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119547206</v>
+        <v>119547149</v>
       </c>
       <c r="B126" t="n">
-        <v>97928</v>
+        <v>79635</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -17700,54 +17722,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500058</v>
+        <v>500053</v>
       </c>
       <c r="R126" t="n">
-        <v>7014017</v>
+        <v>7014032</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -17780,11 +17785,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -16083,10 +16083,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119546175</v>
+        <v>119547929</v>
       </c>
       <c r="B114" t="n">
-        <v>97824</v>
+        <v>96862</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -16099,36 +16099,36 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -16143,10 +16143,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>500096</v>
+        <v>500035</v>
       </c>
       <c r="R114" t="n">
-        <v>7014027</v>
+        <v>7013945</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 1 st skott/stjälk med överblommad blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Särskilt riklig utbredning av revlummer som här dominerar i stor del av fältskiktet inom minst 40 m2.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -16221,7 +16221,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119547116</v>
+        <v>119547206</v>
       </c>
       <c r="B115" t="n">
         <v>97928</v>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -16281,10 +16281,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>500053</v>
+        <v>500058</v>
       </c>
       <c r="R115" t="n">
-        <v>7014032</v>
+        <v>7014017</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -16321,7 +16321,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 21 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -16359,10 +16359,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119546892</v>
+        <v>119550025</v>
       </c>
       <c r="B116" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -16375,21 +16375,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -16419,13 +16419,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>500110</v>
+        <v>500118</v>
       </c>
       <c r="R116" t="n">
-        <v>7014062</v>
+        <v>7013961</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 4 st skott/stjälkar med överblommade blomstänglar inom ca 2 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -16497,7 +16497,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119546089</v>
+        <v>119552989</v>
       </c>
       <c r="B117" t="n">
         <v>97928</v>
@@ -16530,16 +16530,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>gulnande löv/blad</t>
@@ -16557,10 +16549,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>500098</v>
+        <v>499965</v>
       </c>
       <c r="R117" t="n">
-        <v>7014055</v>
+        <v>7013893</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -16587,17 +16579,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 3 st skott av spindelblomster inom ca 1 m2 yta. Arten finns relativt allmänt i skogsbeståndet här. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster finns allmänt i skogsbeståndet där fyndplatsen ligger. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -16617,7 +16609,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd. På frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -16635,10 +16627,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119546264</v>
+        <v>119546175</v>
       </c>
       <c r="B118" t="n">
-        <v>97928</v>
+        <v>97824</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -16651,28 +16643,36 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Spindelblomster finns relativt allmänt i skogsbeståndet här. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 1 st skott/stjälk med överblommad blomstängel. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16765,10 +16765,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119546219</v>
+        <v>119546892</v>
       </c>
       <c r="B119" t="n">
-        <v>78526</v>
+        <v>97824</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16777,44 +16777,61 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>500096</v>
+        <v>500110</v>
       </c>
       <c r="R119" t="n">
-        <v>7014027</v>
+        <v>7014062</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -16848,7 +16865,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 4 st skott/stjälkar med överblommade blomstänglar inom ca 2 m2 yta. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16868,7 +16885,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Luckig grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16886,7 +16903,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119552989</v>
+        <v>119546264</v>
       </c>
       <c r="B120" t="n">
         <v>97928</v>
@@ -16938,10 +16955,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>499965</v>
+        <v>500096</v>
       </c>
       <c r="R120" t="n">
-        <v>7013893</v>
+        <v>7014027</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16968,17 +16985,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Spindelblomster finns allmänt i skogsbeståndet där fyndplatsen ligger. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Spindelblomster finns relativt allmänt i skogsbeståndet här. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -16998,7 +17015,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd. På frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -17016,10 +17033,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119547394</v>
+        <v>119546089</v>
       </c>
       <c r="B121" t="n">
-        <v>97907</v>
+        <v>97928</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -17028,30 +17045,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -17061,7 +17078,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -17076,13 +17093,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>500054</v>
+        <v>500098</v>
       </c>
       <c r="R121" t="n">
-        <v>7013984</v>
+        <v>7014055</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -17116,7 +17133,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Knärot med minst 82 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 3 st skott av spindelblomster inom ca 1 m2 yta. Arten finns relativt allmänt i skogsbeståndet här. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -17136,7 +17153,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -17154,10 +17171,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119550025</v>
+        <v>119547394</v>
       </c>
       <c r="B122" t="n">
-        <v>97928</v>
+        <v>97907</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -17166,30 +17183,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -17199,7 +17216,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -17214,13 +17231,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>500118</v>
+        <v>500054</v>
       </c>
       <c r="R122" t="n">
-        <v>7013961</v>
+        <v>7013984</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -17254,7 +17271,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 82 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -17274,7 +17291,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -17430,10 +17447,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119547929</v>
+        <v>119547149</v>
       </c>
       <c r="B124" t="n">
-        <v>96862</v>
+        <v>79635</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -17446,57 +17463,40 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>500035</v>
+        <v>500053</v>
       </c>
       <c r="R124" t="n">
-        <v>7013945</v>
+        <v>7014032</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -17526,11 +17526,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Särskilt riklig utbredning av revlummer som här dominerar i stor del av fältskiktet inom minst 40 m2.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -17550,7 +17545,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -17568,10 +17563,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119547206</v>
+        <v>119546219</v>
       </c>
       <c r="B125" t="n">
-        <v>97928</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -17580,61 +17575,44 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>500058</v>
+        <v>500096</v>
       </c>
       <c r="R125" t="n">
-        <v>7014017</v>
+        <v>7014027</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -17668,7 +17646,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 4 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav som växer i en gran precis över en grupp med guckusko-plantor. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -17688,7 +17666,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka med högörter och fräken i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -17706,10 +17684,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119547149</v>
+        <v>119545934</v>
       </c>
       <c r="B126" t="n">
-        <v>79635</v>
+        <v>97907</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -17718,44 +17696,61 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>500053</v>
+        <v>500098</v>
       </c>
       <c r="R126" t="n">
-        <v>7014032</v>
+        <v>7014055</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -17785,6 +17780,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Knärot med minst 31 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -17822,10 +17822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119545934</v>
+        <v>119546050</v>
       </c>
       <c r="B127" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -17834,30 +17834,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Knärot med minst 31 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fläcknycklar med minst 2 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -17960,10 +17960,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119546050</v>
+        <v>119547116</v>
       </c>
       <c r="B128" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -17976,26 +17976,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -18005,7 +18005,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -18020,13 +18020,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>500098</v>
+        <v>500053</v>
       </c>
       <c r="R128" t="n">
-        <v>7014055</v>
+        <v>7014032</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Fläcknycklar med minst 2 st skott/stjälkar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Spindelblomster med minst 21 skott/stjälkar inom ca 1 m2. Arten förekommer relativt allmänt i skogsbeståndet. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>En lucka i grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk-fuktig och frisk mark.</t>
+          <t>Grandominerad luckig gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -18098,7 +18098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119300367</v>
+        <v>119300464</v>
       </c>
       <c r="B129" t="n">
         <v>90106</v>
@@ -18133,7 +18133,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>500134</v>
+        <v>500147</v>
       </c>
       <c r="R129" t="n">
-        <v>7013881</v>
+        <v>7013856</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Minst 1 st fruktkropp av gultoppig fingersvamp. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 5 st. fruktkroppar av gultoppig fingersvamp. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -18227,7 +18227,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119300464</v>
+        <v>119300367</v>
       </c>
       <c r="B130" t="n">
         <v>90106</v>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -18278,10 +18278,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>500147</v>
+        <v>500134</v>
       </c>
       <c r="R130" t="n">
-        <v>7013856</v>
+        <v>7013881</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av gultoppig fingersvamp. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 1 st fruktkropp av gultoppig fingersvamp. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -24834,10 +24834,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121339991</v>
+        <v>121338977</v>
       </c>
       <c r="B177" t="n">
-        <v>90705</v>
+        <v>98071</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24846,44 +24846,61 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500281</v>
+        <v>500191</v>
       </c>
       <c r="R177" t="n">
-        <v>7013721</v>
+        <v>7014126</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24917,7 +24934,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24937,27 +24954,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24975,10 +24972,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121338977</v>
+        <v>121339991</v>
       </c>
       <c r="B178" t="n">
-        <v>98071</v>
+        <v>90705</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -24987,61 +24984,44 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500191</v>
+        <v>500281</v>
       </c>
       <c r="R178" t="n">
-        <v>7014126</v>
+        <v>7013721</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -25075,7 +25055,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25095,7 +25075,27 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25251,10 +25251,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121339861</v>
+        <v>121339649</v>
       </c>
       <c r="B180" t="n">
-        <v>78598</v>
+        <v>98071</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25263,41 +25263,58 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500140</v>
+        <v>500207</v>
       </c>
       <c r="R180" t="n">
-        <v>7013999</v>
+        <v>7013937</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -25334,7 +25351,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25354,32 +25371,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL180" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25397,7 +25389,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121339649</v>
+        <v>121339956</v>
       </c>
       <c r="B181" t="n">
         <v>98071</v>
@@ -25432,7 +25424,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -25442,7 +25434,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -25457,13 +25449,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500207</v>
+        <v>500265</v>
       </c>
       <c r="R181" t="n">
-        <v>7013937</v>
+        <v>7013735</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -25497,7 +25489,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25517,7 +25509,7 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25535,10 +25527,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339956</v>
+        <v>121339861</v>
       </c>
       <c r="B182" t="n">
-        <v>98071</v>
+        <v>78598</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25547,61 +25539,44 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500265</v>
+        <v>500140</v>
       </c>
       <c r="R182" t="n">
-        <v>7013735</v>
+        <v>7013999</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -25635,7 +25610,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25656,6 +25631,31 @@
       <c r="AI182" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -18513,7 +18513,7 @@
         <v>120810300</v>
       </c>
       <c r="B132" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>120810369</v>
       </c>
       <c r="B133" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -18781,10 +18781,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121082732</v>
+        <v>121086004</v>
       </c>
       <c r="B134" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -18793,41 +18793,58 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500776</v>
+        <v>500853</v>
       </c>
       <c r="R134" t="n">
-        <v>7013871</v>
+        <v>7013862</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -18864,7 +18881,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st. skott/stjälkar och 2 st. fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -18885,26 +18902,6 @@
       <c r="AI134" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -18922,10 +18919,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121081860</v>
+        <v>121082732</v>
       </c>
       <c r="B135" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -18965,10 +18962,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500786</v>
+        <v>500776</v>
       </c>
       <c r="R135" t="n">
-        <v>7013863</v>
+        <v>7013871</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -19063,10 +19060,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121082671</v>
+        <v>121085785</v>
       </c>
       <c r="B136" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -19098,7 +19095,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19108,7 +19105,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -19119,14 +19116,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500776</v>
+        <v>500828</v>
       </c>
       <c r="R136" t="n">
-        <v>7013871</v>
+        <v>7013875</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -19163,7 +19160,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Knärot med minst 130 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19201,10 +19198,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121086728</v>
+        <v>121086197</v>
       </c>
       <c r="B137" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -19236,7 +19233,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19261,10 +19258,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500895</v>
+        <v>500913</v>
       </c>
       <c r="R137" t="n">
-        <v>7013833</v>
+        <v>7013871</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -19301,7 +19298,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -19321,7 +19318,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -19339,10 +19336,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121082022</v>
+        <v>121086728</v>
       </c>
       <c r="B138" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -19351,35 +19348,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N138" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19387,14 +19392,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500784</v>
+        <v>500895</v>
       </c>
       <c r="R138" t="n">
-        <v>7013868</v>
+        <v>7013833</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -19431,7 +19436,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -19440,6 +19445,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -19450,22 +19456,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -19483,10 +19474,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121086004</v>
+        <v>121086141</v>
       </c>
       <c r="B139" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -19495,58 +19486,45 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500853</v>
+        <v>500882</v>
       </c>
       <c r="R139" t="n">
-        <v>7013862</v>
+        <v>7013873</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -19583,7 +19561,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st. skott/stjälkar och 2 st. fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -19603,7 +19581,32 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -19621,10 +19624,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121085785</v>
+        <v>121081304</v>
       </c>
       <c r="B140" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -19656,7 +19659,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -19681,10 +19684,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500828</v>
+        <v>500622</v>
       </c>
       <c r="R140" t="n">
-        <v>7013875</v>
+        <v>7013801</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -19721,7 +19724,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -19741,7 +19744,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -19759,10 +19762,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121081765</v>
+        <v>121082256</v>
       </c>
       <c r="B141" t="n">
-        <v>57501</v>
+        <v>57351</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -19775,50 +19778,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500786</v>
+        <v>500776</v>
       </c>
       <c r="R141" t="n">
-        <v>7013863</v>
+        <v>7013871</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -19855,7 +19850,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -19875,6 +19870,26 @@
       <c r="AI141" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -19892,10 +19907,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121081304</v>
+        <v>121082671</v>
       </c>
       <c r="B142" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -19927,7 +19942,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -19937,7 +19952,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -19948,14 +19963,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500622</v>
+        <v>500776</v>
       </c>
       <c r="R142" t="n">
-        <v>7013801</v>
+        <v>7013871</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -19992,7 +20007,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 130 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -20012,7 +20027,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -20030,10 +20045,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121086197</v>
+        <v>121081860</v>
       </c>
       <c r="B143" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -20042,58 +20057,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500913</v>
+        <v>500786</v>
       </c>
       <c r="R143" t="n">
-        <v>7013871</v>
+        <v>7013863</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -20130,7 +20128,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -20150,7 +20148,27 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -20168,10 +20186,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121082256</v>
+        <v>121086682</v>
       </c>
       <c r="B144" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -20180,46 +20198,58 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500776</v>
+        <v>500914</v>
       </c>
       <c r="R144" t="n">
-        <v>7013871</v>
+        <v>7013834</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -20256,7 +20286,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -20265,6 +20295,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -20275,27 +20306,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -20313,10 +20324,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121086141</v>
+        <v>121082022</v>
       </c>
       <c r="B145" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -20329,41 +20340,46 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500882</v>
+        <v>500784</v>
       </c>
       <c r="R145" t="n">
-        <v>7013873</v>
+        <v>7013868</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -20400,7 +20416,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -20409,7 +20425,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -20420,32 +20435,22 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -20463,10 +20468,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121081815</v>
+        <v>121081560</v>
       </c>
       <c r="B146" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -20475,58 +20480,41 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500786</v>
+        <v>500739</v>
       </c>
       <c r="R146" t="n">
-        <v>7013863</v>
+        <v>7013841</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -20563,7 +20551,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -20584,6 +20572,26 @@
       <c r="AI146" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -20601,10 +20609,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121086682</v>
+        <v>121081765</v>
       </c>
       <c r="B147" t="n">
-        <v>98071</v>
+        <v>57504</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -20613,43 +20621,39 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -20657,14 +20661,14 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500914</v>
+        <v>500786</v>
       </c>
       <c r="R147" t="n">
-        <v>7013834</v>
+        <v>7013863</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -20701,7 +20705,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -20710,7 +20714,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -20721,7 +20724,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -20739,10 +20742,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121080224</v>
+        <v>121081815</v>
       </c>
       <c r="B148" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -20774,7 +20777,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -20784,7 +20787,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -20795,17 +20798,17 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500615</v>
+        <v>500786</v>
       </c>
       <c r="R148" t="n">
-        <v>7013796</v>
+        <v>7013863</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -20839,7 +20842,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -20859,7 +20862,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -20877,10 +20880,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121081560</v>
+        <v>121080224</v>
       </c>
       <c r="B149" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -20889,44 +20892,61 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500739</v>
+        <v>500615</v>
       </c>
       <c r="R149" t="n">
-        <v>7013841</v>
+        <v>7013796</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -20960,7 +20980,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -20980,27 +21000,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -21018,10 +21018,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121201394</v>
+        <v>121195472</v>
       </c>
       <c r="B150" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500242</v>
+        <v>500883</v>
       </c>
       <c r="R150" t="n">
-        <v>7013801</v>
+        <v>7013806</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -21108,17 +21108,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21156,10 +21156,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121197538</v>
+        <v>121203688</v>
       </c>
       <c r="B151" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21201,7 +21201,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -21216,13 +21216,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500895</v>
+        <v>500200</v>
       </c>
       <c r="R151" t="n">
-        <v>7013735</v>
+        <v>7014080</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -21246,17 +21246,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121201748</v>
+        <v>121201641</v>
       </c>
       <c r="B152" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21354,10 +21354,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500205</v>
+        <v>500241</v>
       </c>
       <c r="R152" t="n">
-        <v>7013878</v>
+        <v>7013834</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -21394,7 +21394,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21432,10 +21432,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121203724</v>
+        <v>121196283</v>
       </c>
       <c r="B153" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21492,10 +21492,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500179</v>
+        <v>500872</v>
       </c>
       <c r="R153" t="n">
-        <v>7013960</v>
+        <v>7013820</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -21522,17 +21522,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21552,7 +21552,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21570,10 +21570,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121196729</v>
+        <v>121201836</v>
       </c>
       <c r="B154" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -21630,10 +21630,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500833</v>
+        <v>500162</v>
       </c>
       <c r="R154" t="n">
-        <v>7013748</v>
+        <v>7013924</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -21660,17 +21660,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -21708,10 +21708,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121201641</v>
+        <v>121197538</v>
       </c>
       <c r="B155" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -21753,7 +21753,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -21768,10 +21768,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500241</v>
+        <v>500895</v>
       </c>
       <c r="R155" t="n">
-        <v>7013834</v>
+        <v>7013735</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -21798,17 +21798,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -21846,10 +21846,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121196381</v>
+        <v>121198065</v>
       </c>
       <c r="B156" t="n">
-        <v>79708</v>
+        <v>98081</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21858,45 +21858,58 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500872</v>
+        <v>500857</v>
       </c>
       <c r="R156" t="n">
-        <v>7013820</v>
+        <v>7013723</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -21933,7 +21946,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -21953,32 +21966,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL156" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -21996,10 +21984,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121195472</v>
+        <v>121203565</v>
       </c>
       <c r="B157" t="n">
-        <v>98071</v>
+        <v>97998</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -22008,30 +21996,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -22045,24 +22033,20 @@
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500883</v>
+        <v>500210</v>
       </c>
       <c r="R157" t="n">
-        <v>7013806</v>
+        <v>7014055</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -22086,17 +22070,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22116,7 +22100,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22134,10 +22118,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121196322</v>
+        <v>121196381</v>
       </c>
       <c r="B158" t="n">
-        <v>79679</v>
+        <v>79711</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -22146,32 +22130,32 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -22221,7 +22205,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -22241,7 +22225,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
@@ -22256,7 +22240,7 @@
       </c>
       <c r="AL158" t="inlineStr">
         <is>
-          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
@@ -22264,12 +22248,9 @@
           <t>Bark på levande träd</t>
         </is>
       </c>
-      <c r="AN158" t="n">
-        <v>2</v>
-      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -22287,10 +22268,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121197288</v>
+        <v>121203724</v>
       </c>
       <c r="B159" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -22299,45 +22280,58 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500924</v>
+        <v>500179</v>
       </c>
       <c r="R159" t="n">
-        <v>7013754</v>
+        <v>7013960</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22364,17 +22358,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22394,32 +22388,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL159" t="inlineStr">
-        <is>
-          <t>En skadad död stående sälgstam.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -22437,10 +22406,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121196283</v>
+        <v>121196322</v>
       </c>
       <c r="B160" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -22449,48 +22418,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
@@ -22537,7 +22493,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22557,7 +22513,35 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -22575,10 +22559,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121203688</v>
+        <v>121201394</v>
       </c>
       <c r="B161" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -22610,7 +22594,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -22635,13 +22619,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>500200</v>
+        <v>500242</v>
       </c>
       <c r="R161" t="n">
-        <v>7014080</v>
+        <v>7013801</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -22675,7 +22659,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -22695,7 +22679,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -22713,10 +22697,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121198065</v>
+        <v>121201748</v>
       </c>
       <c r="B162" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -22748,7 +22732,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -22773,10 +22757,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>500857</v>
+        <v>500205</v>
       </c>
       <c r="R162" t="n">
-        <v>7013723</v>
+        <v>7013878</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -22803,17 +22787,17 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -22833,7 +22817,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -22851,10 +22835,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121203565</v>
+        <v>121196729</v>
       </c>
       <c r="B163" t="n">
-        <v>97988</v>
+        <v>98081</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -22863,30 +22847,30 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22900,20 +22884,24 @@
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500210</v>
+        <v>500833</v>
       </c>
       <c r="R163" t="n">
-        <v>7014055</v>
+        <v>7013748</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -22937,17 +22925,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22967,7 +22955,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22985,10 +22973,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121201836</v>
+        <v>121197288</v>
       </c>
       <c r="B164" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -22997,58 +22985,45 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500162</v>
+        <v>500924</v>
       </c>
       <c r="R164" t="n">
-        <v>7013924</v>
+        <v>7013754</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -23075,17 +23050,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23105,7 +23080,32 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318594</v>
+        <v>121318473</v>
       </c>
       <c r="B165" t="n">
-        <v>57501</v>
+        <v>90693</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,50 +23139,45 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R165" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -23228,6 +23223,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23238,7 +23234,27 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23259,7 +23275,7 @@
         <v>121318402</v>
       </c>
       <c r="B166" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -23389,10 +23405,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318473</v>
+        <v>121318594</v>
       </c>
       <c r="B167" t="n">
-        <v>90683</v>
+        <v>57504</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23405,45 +23421,50 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R167" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -23489,7 +23510,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -23500,27 +23520,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121335603</v>
+        <v>121339038</v>
       </c>
       <c r="B168" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,35 +23550,43 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N168" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -23586,14 +23594,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500182</v>
+        <v>500173</v>
       </c>
       <c r="R168" t="n">
-        <v>7014067</v>
+        <v>7014080</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23630,7 +23638,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23639,6 +23647,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -23649,27 +23658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23687,10 +23676,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339891</v>
+        <v>121339476</v>
       </c>
       <c r="B169" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23699,35 +23688,43 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -23735,14 +23732,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500163</v>
+        <v>500200</v>
       </c>
       <c r="R169" t="n">
-        <v>7013970</v>
+        <v>7014028</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -23779,7 +23776,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23788,6 +23785,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -23798,27 +23796,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23836,10 +23814,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339542</v>
+        <v>121339891</v>
       </c>
       <c r="B170" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23852,52 +23830,49 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500188</v>
+        <v>500163</v>
       </c>
       <c r="R170" t="n">
-        <v>7013973</v>
+        <v>7013970</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -23931,7 +23906,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23940,7 +23915,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -23951,7 +23925,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
@@ -23966,12 +23940,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23989,10 +23963,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339782</v>
+        <v>121339542</v>
       </c>
       <c r="B171" t="n">
-        <v>98071</v>
+        <v>90715</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -24001,61 +23975,56 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500152</v>
+        <v>500188</v>
       </c>
       <c r="R171" t="n">
-        <v>7013957</v>
+        <v>7013973</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24089,7 +24058,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24109,7 +24078,27 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24127,10 +24116,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121338927</v>
+        <v>121338977</v>
       </c>
       <c r="B172" t="n">
-        <v>97988</v>
+        <v>98081</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24139,30 +24128,30 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -24172,7 +24161,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
@@ -24187,10 +24176,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500220</v>
+        <v>500191</v>
       </c>
       <c r="R172" t="n">
-        <v>7014127</v>
+        <v>7014126</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -24227,7 +24216,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24265,10 +24254,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121339897</v>
+        <v>121339861</v>
       </c>
       <c r="B173" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24277,58 +24266,41 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500163</v>
+        <v>500140</v>
       </c>
       <c r="R173" t="n">
-        <v>7013970</v>
+        <v>7013999</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24365,7 +24337,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24386,6 +24358,31 @@
       <c r="AI173" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24406,7 +24403,7 @@
         <v>121340000</v>
       </c>
       <c r="B174" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24548,10 +24545,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121339476</v>
+        <v>121335603</v>
       </c>
       <c r="B175" t="n">
-        <v>98071</v>
+        <v>57351</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24560,43 +24557,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24604,14 +24593,14 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500200</v>
+        <v>500182</v>
       </c>
       <c r="R175" t="n">
-        <v>7014028</v>
+        <v>7014067</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -24648,7 +24637,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24657,7 +24646,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -24668,7 +24656,27 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24686,10 +24694,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339923</v>
+        <v>121339991</v>
       </c>
       <c r="B176" t="n">
-        <v>91370</v>
+        <v>90715</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24698,42 +24706,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
@@ -24741,10 +24737,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500108</v>
+        <v>500281</v>
       </c>
       <c r="R176" t="n">
-        <v>7013909</v>
+        <v>7013721</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24779,6 +24775,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -24811,12 +24812,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24834,10 +24835,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121338977</v>
+        <v>121339649</v>
       </c>
       <c r="B177" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24869,7 +24870,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -24894,13 +24895,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500191</v>
+        <v>500207</v>
       </c>
       <c r="R177" t="n">
-        <v>7014126</v>
+        <v>7013937</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24934,7 +24935,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24954,7 +24955,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24972,10 +24973,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121339991</v>
+        <v>121339744</v>
       </c>
       <c r="B178" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -25005,9 +25006,21 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
@@ -25015,10 +25028,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500281</v>
+        <v>500169</v>
       </c>
       <c r="R178" t="n">
-        <v>7013721</v>
+        <v>7013982</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -25055,7 +25068,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25075,7 +25088,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
@@ -25090,12 +25103,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25113,10 +25126,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121339038</v>
+        <v>121339923</v>
       </c>
       <c r="B179" t="n">
-        <v>98071</v>
+        <v>91380</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25125,58 +25138,53 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500173</v>
+        <v>500108</v>
       </c>
       <c r="R179" t="n">
-        <v>7014080</v>
+        <v>7013909</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -25211,11 +25219,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -25233,7 +25236,27 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25251,10 +25274,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121339649</v>
+        <v>121335375</v>
       </c>
       <c r="B180" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25286,7 +25309,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -25296,7 +25319,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -25311,10 +25334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500207</v>
+        <v>500170</v>
       </c>
       <c r="R180" t="n">
-        <v>7013937</v>
+        <v>7014032</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -25351,7 +25374,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25371,7 +25394,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25389,10 +25412,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121339956</v>
+        <v>121337877</v>
       </c>
       <c r="B181" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25424,7 +25447,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -25449,10 +25472,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500265</v>
+        <v>500184</v>
       </c>
       <c r="R181" t="n">
-        <v>7013735</v>
+        <v>7014123</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25489,7 +25512,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25509,7 +25532,7 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25527,10 +25550,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339861</v>
+        <v>121339782</v>
       </c>
       <c r="B182" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25539,41 +25562,58 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500140</v>
+        <v>500152</v>
       </c>
       <c r="R182" t="n">
-        <v>7013999</v>
+        <v>7013957</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -25610,7 +25650,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25630,32 +25670,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL182" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25673,10 +25688,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339744</v>
+        <v>121339956</v>
       </c>
       <c r="B183" t="n">
-        <v>90705</v>
+        <v>98081</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25685,56 +25700,61 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500169</v>
+        <v>500265</v>
       </c>
       <c r="R183" t="n">
-        <v>7013982</v>
+        <v>7013735</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -25768,7 +25788,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25788,27 +25808,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25826,10 +25826,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121337877</v>
+        <v>121338927</v>
       </c>
       <c r="B184" t="n">
-        <v>98071</v>
+        <v>97998</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25838,30 +25838,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25886,10 +25886,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500184</v>
+        <v>500220</v>
       </c>
       <c r="R184" t="n">
-        <v>7014123</v>
+        <v>7014127</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25964,10 +25964,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121335375</v>
+        <v>121339897</v>
       </c>
       <c r="B185" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -26020,14 +26020,14 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500170</v>
+        <v>500163</v>
       </c>
       <c r="R185" t="n">
-        <v>7014032</v>
+        <v>7013970</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -26064,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -19624,10 +19624,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121081304</v>
+        <v>121082256</v>
       </c>
       <c r="B140" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -19636,58 +19636,46 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500622</v>
+        <v>500776</v>
       </c>
       <c r="R140" t="n">
-        <v>7013801</v>
+        <v>7013871</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -19724,7 +19712,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -19733,7 +19721,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -19744,7 +19731,27 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -19762,10 +19769,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121082256</v>
+        <v>121081304</v>
       </c>
       <c r="B141" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -19774,46 +19781,58 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500776</v>
+        <v>500622</v>
       </c>
       <c r="R141" t="n">
-        <v>7013871</v>
+        <v>7013801</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -19850,7 +19869,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -19859,6 +19878,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -19869,27 +19889,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -19624,10 +19624,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121082256</v>
+        <v>121081304</v>
       </c>
       <c r="B140" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -19636,46 +19636,58 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500776</v>
+        <v>500622</v>
       </c>
       <c r="R140" t="n">
-        <v>7013871</v>
+        <v>7013801</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -19712,7 +19724,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -19721,6 +19733,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -19731,27 +19744,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -19769,10 +19762,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121081304</v>
+        <v>121082256</v>
       </c>
       <c r="B141" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -19781,58 +19774,46 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500622</v>
+        <v>500776</v>
       </c>
       <c r="R141" t="n">
-        <v>7013801</v>
+        <v>7013871</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -19869,7 +19850,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -19878,7 +19859,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -19889,7 +19869,27 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -18919,10 +18919,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121082732</v>
+        <v>121086728</v>
       </c>
       <c r="B135" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -18931,41 +18931,58 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500776</v>
+        <v>500895</v>
       </c>
       <c r="R135" t="n">
-        <v>7013871</v>
+        <v>7013833</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -19002,7 +19019,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -19022,27 +19039,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -19060,10 +19057,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121085785</v>
+        <v>121081560</v>
       </c>
       <c r="B136" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -19072,58 +19069,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500828</v>
+        <v>500739</v>
       </c>
       <c r="R136" t="n">
-        <v>7013875</v>
+        <v>7013841</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -19160,7 +19140,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19181,6 +19161,26 @@
       <c r="AI136" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121086197</v>
+        <v>121086682</v>
       </c>
       <c r="B137" t="n">
         <v>98081</v>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -19258,10 +19258,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500913</v>
+        <v>500914</v>
       </c>
       <c r="R137" t="n">
-        <v>7013871</v>
+        <v>7013834</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -19336,10 +19336,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121086728</v>
+        <v>121082022</v>
       </c>
       <c r="B138" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -19348,43 +19348,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19392,14 +19384,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500895</v>
+        <v>500784</v>
       </c>
       <c r="R138" t="n">
-        <v>7013833</v>
+        <v>7013868</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -19436,7 +19428,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -19445,7 +19437,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -19456,7 +19447,22 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -19474,10 +19480,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121086141</v>
+        <v>121085785</v>
       </c>
       <c r="B139" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -19486,45 +19492,58 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500882</v>
+        <v>500828</v>
       </c>
       <c r="R139" t="n">
-        <v>7013873</v>
+        <v>7013875</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -19561,7 +19580,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -19581,32 +19600,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -19624,7 +19618,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121081304</v>
+        <v>121082671</v>
       </c>
       <c r="B140" t="n">
         <v>98081</v>
@@ -19659,7 +19653,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -19669,7 +19663,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -19680,14 +19674,14 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500622</v>
+        <v>500776</v>
       </c>
       <c r="R140" t="n">
-        <v>7013801</v>
+        <v>7013871</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -19724,7 +19718,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 130 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -19744,7 +19738,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -19762,10 +19756,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121082256</v>
+        <v>121081765</v>
       </c>
       <c r="B141" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -19778,42 +19772,50 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500776</v>
+        <v>500786</v>
       </c>
       <c r="R141" t="n">
-        <v>7013871</v>
+        <v>7013863</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -19850,7 +19852,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -19870,26 +19872,6 @@
       <c r="AI141" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -19907,7 +19889,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121082671</v>
+        <v>121081304</v>
       </c>
       <c r="B142" t="n">
         <v>98081</v>
@@ -19942,7 +19924,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -19952,7 +19934,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -19963,14 +19945,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500776</v>
+        <v>500622</v>
       </c>
       <c r="R142" t="n">
-        <v>7013871</v>
+        <v>7013801</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -20007,7 +19989,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Knärot med minst 130 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -20027,7 +20009,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -20045,10 +20027,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121081860</v>
+        <v>121086197</v>
       </c>
       <c r="B143" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -20057,41 +20039,58 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500786</v>
+        <v>500913</v>
       </c>
       <c r="R143" t="n">
-        <v>7013863</v>
+        <v>7013871</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -20128,7 +20127,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -20148,27 +20147,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -20186,7 +20165,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121086682</v>
+        <v>121081815</v>
       </c>
       <c r="B144" t="n">
         <v>98081</v>
@@ -20221,7 +20200,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -20242,14 +20221,14 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500914</v>
+        <v>500786</v>
       </c>
       <c r="R144" t="n">
-        <v>7013834</v>
+        <v>7013863</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -20286,7 +20265,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -20306,7 +20285,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -20324,10 +20303,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121082022</v>
+        <v>121086141</v>
       </c>
       <c r="B145" t="n">
-        <v>57351</v>
+        <v>79682</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -20340,46 +20319,41 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500784</v>
+        <v>500882</v>
       </c>
       <c r="R145" t="n">
-        <v>7013868</v>
+        <v>7013873</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -20416,7 +20390,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -20425,6 +20399,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -20435,22 +20410,32 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -20468,10 +20453,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121081560</v>
+        <v>121080224</v>
       </c>
       <c r="B146" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -20480,44 +20465,61 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500739</v>
+        <v>500615</v>
       </c>
       <c r="R146" t="n">
-        <v>7013841</v>
+        <v>7013796</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -20551,7 +20553,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -20571,27 +20573,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -20609,10 +20591,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121081765</v>
+        <v>121081860</v>
       </c>
       <c r="B147" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -20625,40 +20607,27 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
@@ -20705,7 +20674,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -20714,6 +20683,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -20725,6 +20695,26 @@
       <c r="AI147" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -20742,10 +20732,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121081815</v>
+        <v>121082732</v>
       </c>
       <c r="B148" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -20754,58 +20744,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500786</v>
+        <v>500776</v>
       </c>
       <c r="R148" t="n">
-        <v>7013863</v>
+        <v>7013871</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -20842,7 +20815,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -20863,6 +20836,26 @@
       <c r="AI148" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -20880,10 +20873,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121080224</v>
+        <v>121082256</v>
       </c>
       <c r="B149" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -20892,61 +20885,49 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>500615</v>
+        <v>500776</v>
       </c>
       <c r="R149" t="n">
-        <v>7013796</v>
+        <v>7013871</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -20980,7 +20961,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -20989,7 +20970,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -21000,7 +20980,27 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -21018,7 +21018,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121195472</v>
+        <v>121196283</v>
       </c>
       <c r="B150" t="n">
         <v>98081</v>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500883</v>
+        <v>500872</v>
       </c>
       <c r="R150" t="n">
-        <v>7013806</v>
+        <v>7013820</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21156,7 +21156,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121203688</v>
+        <v>121201394</v>
       </c>
       <c r="B151" t="n">
         <v>98081</v>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21216,13 +21216,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500200</v>
+        <v>500242</v>
       </c>
       <c r="R151" t="n">
-        <v>7014080</v>
+        <v>7013801</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -21294,7 +21294,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121201641</v>
+        <v>121201748</v>
       </c>
       <c r="B152" t="n">
         <v>98081</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21354,10 +21354,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500241</v>
+        <v>500205</v>
       </c>
       <c r="R152" t="n">
-        <v>7013834</v>
+        <v>7013878</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -21394,7 +21394,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21432,7 +21432,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121196283</v>
+        <v>121196729</v>
       </c>
       <c r="B153" t="n">
         <v>98081</v>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21492,10 +21492,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500872</v>
+        <v>500833</v>
       </c>
       <c r="R153" t="n">
-        <v>7013820</v>
+        <v>7013748</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21552,7 +21552,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21570,10 +21570,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121201836</v>
+        <v>121196381</v>
       </c>
       <c r="B154" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -21582,58 +21582,45 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500162</v>
+        <v>500872</v>
       </c>
       <c r="R154" t="n">
-        <v>7013924</v>
+        <v>7013820</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -21660,17 +21647,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -21690,7 +21677,32 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>En lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -21708,10 +21720,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121197538</v>
+        <v>121197288</v>
       </c>
       <c r="B155" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -21720,58 +21732,45 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500895</v>
+        <v>500924</v>
       </c>
       <c r="R155" t="n">
-        <v>7013735</v>
+        <v>7013754</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -21808,7 +21807,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -21828,7 +21827,32 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -21846,10 +21870,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121198065</v>
+        <v>121196322</v>
       </c>
       <c r="B156" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21858,58 +21882,45 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500857</v>
+        <v>500872</v>
       </c>
       <c r="R156" t="n">
-        <v>7013723</v>
+        <v>7013820</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -21946,7 +21957,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -21966,7 +21977,35 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -21984,10 +22023,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121203565</v>
+        <v>121203688</v>
       </c>
       <c r="B157" t="n">
-        <v>97998</v>
+        <v>98081</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -21996,30 +22035,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -22033,17 +22072,21 @@
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500210</v>
+        <v>500200</v>
       </c>
       <c r="R157" t="n">
-        <v>7014055</v>
+        <v>7014080</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -22080,7 +22123,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22100,7 +22143,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22118,10 +22161,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121196381</v>
+        <v>121201641</v>
       </c>
       <c r="B158" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -22130,45 +22173,58 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500872</v>
+        <v>500241</v>
       </c>
       <c r="R158" t="n">
-        <v>7013820</v>
+        <v>7013834</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -22195,17 +22251,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -22225,32 +22281,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL158" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -22268,7 +22299,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121203724</v>
+        <v>121197538</v>
       </c>
       <c r="B159" t="n">
         <v>98081</v>
@@ -22303,7 +22334,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -22313,7 +22344,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -22328,10 +22359,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500179</v>
+        <v>500895</v>
       </c>
       <c r="R159" t="n">
-        <v>7013960</v>
+        <v>7013735</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22358,17 +22389,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22388,7 +22419,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -22406,10 +22437,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121196322</v>
+        <v>121195472</v>
       </c>
       <c r="B160" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -22418,45 +22449,58 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500872</v>
+        <v>500883</v>
       </c>
       <c r="R160" t="n">
-        <v>7013820</v>
+        <v>7013806</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -22493,7 +22537,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22514,34 +22558,6 @@
       <c r="AI160" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN160" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -22559,7 +22575,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121201394</v>
+        <v>121198065</v>
       </c>
       <c r="B161" t="n">
         <v>98081</v>
@@ -22594,7 +22610,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -22619,10 +22635,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>500242</v>
+        <v>500857</v>
       </c>
       <c r="R161" t="n">
-        <v>7013801</v>
+        <v>7013723</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -22649,17 +22665,17 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -22679,7 +22695,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -22697,7 +22713,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121201748</v>
+        <v>121201836</v>
       </c>
       <c r="B162" t="n">
         <v>98081</v>
@@ -22732,7 +22748,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -22757,10 +22773,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>500205</v>
+        <v>500162</v>
       </c>
       <c r="R162" t="n">
-        <v>7013878</v>
+        <v>7013924</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -22797,7 +22813,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -22817,7 +22833,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -22835,7 +22851,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121196729</v>
+        <v>121203724</v>
       </c>
       <c r="B163" t="n">
         <v>98081</v>
@@ -22870,7 +22886,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22895,10 +22911,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500833</v>
+        <v>500179</v>
       </c>
       <c r="R163" t="n">
-        <v>7013748</v>
+        <v>7013960</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -22925,17 +22941,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22955,7 +22971,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22973,10 +22989,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121197288</v>
+        <v>121203565</v>
       </c>
       <c r="B164" t="n">
-        <v>79682</v>
+        <v>97998</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -22985,34 +23001,43 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -23020,13 +23045,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500924</v>
+        <v>500210</v>
       </c>
       <c r="R164" t="n">
-        <v>7013754</v>
+        <v>7014055</v>
       </c>
       <c r="S164" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -23050,17 +23075,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23080,32 +23105,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>En skadad död stående sälgstam.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318473</v>
+        <v>121318594</v>
       </c>
       <c r="B165" t="n">
-        <v>90693</v>
+        <v>57504</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,45 +23139,50 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R165" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -23223,7 +23228,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23234,27 +23238,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23405,10 +23389,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318594</v>
+        <v>121318473</v>
       </c>
       <c r="B167" t="n">
-        <v>57504</v>
+        <v>90693</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23421,50 +23405,45 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R167" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -23510,6 +23489,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -23520,7 +23500,27 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121339038</v>
+        <v>121339861</v>
       </c>
       <c r="B168" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,58 +23550,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500173</v>
+        <v>500140</v>
       </c>
       <c r="R168" t="n">
-        <v>7014080</v>
+        <v>7013999</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23638,7 +23621,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23658,7 +23641,32 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23676,10 +23684,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339476</v>
+        <v>121339923</v>
       </c>
       <c r="B169" t="n">
-        <v>98081</v>
+        <v>91380</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23688,58 +23696,53 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500200</v>
+        <v>500108</v>
       </c>
       <c r="R169" t="n">
-        <v>7014028</v>
+        <v>7013909</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -23774,11 +23777,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -23796,7 +23794,27 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23814,10 +23832,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339891</v>
+        <v>121339744</v>
       </c>
       <c r="B170" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23830,46 +23848,49 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500163</v>
+        <v>500169</v>
       </c>
       <c r="R170" t="n">
-        <v>7013970</v>
+        <v>7013982</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -23906,7 +23927,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23915,6 +23936,7 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -23925,7 +23947,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
@@ -23940,12 +23962,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23963,10 +23985,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339542</v>
+        <v>121339897</v>
       </c>
       <c r="B171" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23975,56 +23997,61 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500188</v>
+        <v>500163</v>
       </c>
       <c r="R171" t="n">
-        <v>7013973</v>
+        <v>7013970</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24058,7 +24085,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24078,27 +24105,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24116,7 +24123,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121338977</v>
+        <v>121339956</v>
       </c>
       <c r="B172" t="n">
         <v>98081</v>
@@ -24151,7 +24158,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -24161,7 +24168,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
@@ -24176,10 +24183,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500191</v>
+        <v>500265</v>
       </c>
       <c r="R172" t="n">
-        <v>7014126</v>
+        <v>7013735</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -24216,7 +24223,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24236,7 +24243,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24254,10 +24261,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121339861</v>
+        <v>121335375</v>
       </c>
       <c r="B173" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24266,41 +24273,58 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500140</v>
+        <v>500170</v>
       </c>
       <c r="R173" t="n">
-        <v>7013999</v>
+        <v>7014032</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24337,7 +24361,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24357,32 +24381,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL173" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24400,10 +24399,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121340000</v>
+        <v>121339782</v>
       </c>
       <c r="B174" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24412,48 +24411,61 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500299</v>
+        <v>500152</v>
       </c>
       <c r="R174" t="n">
-        <v>7013696</v>
+        <v>7013957</v>
       </c>
       <c r="S174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -24487,7 +24499,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24507,27 +24519,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24545,10 +24537,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121335603</v>
+        <v>121339542</v>
       </c>
       <c r="B175" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24561,49 +24553,52 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500182</v>
+        <v>500188</v>
       </c>
       <c r="R175" t="n">
-        <v>7014067</v>
+        <v>7013973</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -24637,7 +24632,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24646,6 +24641,7 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -24656,7 +24652,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -24671,12 +24667,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24694,10 +24690,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339991</v>
+        <v>121339891</v>
       </c>
       <c r="B176" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24710,37 +24706,46 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500281</v>
+        <v>500163</v>
       </c>
       <c r="R176" t="n">
-        <v>7013721</v>
+        <v>7013970</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24777,7 +24782,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24786,7 +24791,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -24812,12 +24816,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24835,10 +24839,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121339649</v>
+        <v>121335603</v>
       </c>
       <c r="B177" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24847,43 +24851,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24891,14 +24887,14 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500207</v>
+        <v>500182</v>
       </c>
       <c r="R177" t="n">
-        <v>7013937</v>
+        <v>7014067</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -24935,7 +24931,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24944,7 +24940,6 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -24955,7 +24950,27 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24973,10 +24988,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121339744</v>
+        <v>121337877</v>
       </c>
       <c r="B178" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -24985,56 +25000,61 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500169</v>
+        <v>500184</v>
       </c>
       <c r="R178" t="n">
-        <v>7013982</v>
+        <v>7014123</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -25068,7 +25088,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25088,27 +25108,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25126,10 +25126,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121339923</v>
+        <v>121339649</v>
       </c>
       <c r="B179" t="n">
-        <v>91380</v>
+        <v>98081</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25138,53 +25138,58 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500108</v>
+        <v>500207</v>
       </c>
       <c r="R179" t="n">
-        <v>7013909</v>
+        <v>7013937</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -25219,6 +25224,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -25236,27 +25246,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25274,10 +25264,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121335375</v>
+        <v>121340000</v>
       </c>
       <c r="B180" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25286,61 +25276,48 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500170</v>
+        <v>500299</v>
       </c>
       <c r="R180" t="n">
-        <v>7014032</v>
+        <v>7013696</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -25374,7 +25351,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25394,7 +25371,27 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25412,7 +25409,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121337877</v>
+        <v>121338977</v>
       </c>
       <c r="B181" t="n">
         <v>98081</v>
@@ -25447,7 +25444,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -25457,7 +25454,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -25472,10 +25469,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500184</v>
+        <v>500191</v>
       </c>
       <c r="R181" t="n">
-        <v>7014123</v>
+        <v>7014126</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25512,7 +25509,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25550,10 +25547,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339782</v>
+        <v>121339991</v>
       </c>
       <c r="B182" t="n">
-        <v>98081</v>
+        <v>90715</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25562,58 +25559,41 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500152</v>
+        <v>500281</v>
       </c>
       <c r="R182" t="n">
-        <v>7013957</v>
+        <v>7013721</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -25650,7 +25630,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25670,7 +25650,27 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25688,10 +25688,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339956</v>
+        <v>121338927</v>
       </c>
       <c r="B183" t="n">
-        <v>98081</v>
+        <v>97998</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25700,30 +25700,30 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -25748,10 +25748,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500265</v>
+        <v>500220</v>
       </c>
       <c r="R183" t="n">
-        <v>7013735</v>
+        <v>7014127</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25808,7 +25808,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25826,10 +25826,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121338927</v>
+        <v>121339476</v>
       </c>
       <c r="B184" t="n">
-        <v>97998</v>
+        <v>98081</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25838,30 +25838,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500220</v>
+        <v>500200</v>
       </c>
       <c r="R184" t="n">
-        <v>7014127</v>
+        <v>7014028</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25964,7 +25964,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339897</v>
+        <v>121339038</v>
       </c>
       <c r="B185" t="n">
         <v>98081</v>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -26020,14 +26020,14 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500163</v>
+        <v>500173</v>
       </c>
       <c r="R185" t="n">
-        <v>7013970</v>
+        <v>7014080</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -26064,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -20165,10 +20165,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121081815</v>
+        <v>121086141</v>
       </c>
       <c r="B144" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -20177,58 +20177,45 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500786</v>
+        <v>500882</v>
       </c>
       <c r="R144" t="n">
-        <v>7013863</v>
+        <v>7013873</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -20265,7 +20252,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -20285,7 +20272,32 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -20303,10 +20315,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121086141</v>
+        <v>121081815</v>
       </c>
       <c r="B145" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -20315,45 +20327,58 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500882</v>
+        <v>500786</v>
       </c>
       <c r="R145" t="n">
-        <v>7013873</v>
+        <v>7013863</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -20390,7 +20415,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -20410,32 +20435,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -22851,10 +22851,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121203724</v>
+        <v>121203565</v>
       </c>
       <c r="B163" t="n">
-        <v>98081</v>
+        <v>97998</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -22863,30 +22863,30 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22900,24 +22900,20 @@
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500179</v>
+        <v>500210</v>
       </c>
       <c r="R163" t="n">
-        <v>7013960</v>
+        <v>7014055</v>
       </c>
       <c r="S163" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -22951,7 +22947,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22971,7 +22967,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22989,10 +22985,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121203565</v>
+        <v>121203724</v>
       </c>
       <c r="B164" t="n">
-        <v>97998</v>
+        <v>98081</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -23001,30 +22997,30 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -23038,20 +23034,24 @@
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500210</v>
+        <v>500179</v>
       </c>
       <c r="R164" t="n">
-        <v>7014055</v>
+        <v>7013960</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -18781,10 +18781,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121086004</v>
+        <v>121086682</v>
       </c>
       <c r="B134" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -18841,10 +18841,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500853</v>
+        <v>500914</v>
       </c>
       <c r="R134" t="n">
-        <v>7013862</v>
+        <v>7013834</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st. skott/stjälkar och 2 st. fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -18901,7 +18901,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -18919,10 +18919,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121086728</v>
+        <v>121081815</v>
       </c>
       <c r="B135" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -18975,14 +18975,14 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500895</v>
+        <v>500786</v>
       </c>
       <c r="R135" t="n">
-        <v>7013833</v>
+        <v>7013863</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -19019,7 +19019,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -19057,10 +19057,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121081560</v>
+        <v>121086197</v>
       </c>
       <c r="B136" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -19069,41 +19069,58 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500739</v>
+        <v>500913</v>
       </c>
       <c r="R136" t="n">
-        <v>7013841</v>
+        <v>7013871</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -19140,7 +19157,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19160,27 +19177,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -19198,10 +19195,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121086682</v>
+        <v>121081560</v>
       </c>
       <c r="B137" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -19210,58 +19207,41 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500914</v>
+        <v>500739</v>
       </c>
       <c r="R137" t="n">
-        <v>7013834</v>
+        <v>7013841</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -19298,7 +19278,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -19318,7 +19298,27 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -19336,10 +19336,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121082022</v>
+        <v>121081765</v>
       </c>
       <c r="B138" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -19352,29 +19352,33 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -19388,10 +19392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>500784</v>
+        <v>500786</v>
       </c>
       <c r="R138" t="n">
-        <v>7013868</v>
+        <v>7013863</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -19428,7 +19432,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -19448,21 +19452,6 @@
       <c r="AI138" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -19480,10 +19469,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121085785</v>
+        <v>121082022</v>
       </c>
       <c r="B139" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -19492,43 +19481,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19536,14 +19517,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500828</v>
+        <v>500784</v>
       </c>
       <c r="R139" t="n">
-        <v>7013875</v>
+        <v>7013868</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -19580,7 +19561,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -19589,7 +19570,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -19601,6 +19581,21 @@
       <c r="AI139" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -19618,10 +19613,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121082671</v>
+        <v>121081860</v>
       </c>
       <c r="B140" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -19630,58 +19625,41 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500776</v>
+        <v>500786</v>
       </c>
       <c r="R140" t="n">
-        <v>7013871</v>
+        <v>7013863</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -19718,7 +19696,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Knärot med minst 130 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -19739,6 +19717,26 @@
       <c r="AI140" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -19756,10 +19754,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121081765</v>
+        <v>121082732</v>
       </c>
       <c r="B141" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -19772,50 +19770,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500786</v>
+        <v>500776</v>
       </c>
       <c r="R141" t="n">
-        <v>7013863</v>
+        <v>7013871</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -19852,7 +19837,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -19861,6 +19846,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -19872,6 +19858,26 @@
       <c r="AI141" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -19889,10 +19895,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121081304</v>
+        <v>121086728</v>
       </c>
       <c r="B142" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -19924,7 +19930,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -19934,7 +19940,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -19949,10 +19955,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500622</v>
+        <v>500895</v>
       </c>
       <c r="R142" t="n">
-        <v>7013801</v>
+        <v>7013833</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -19989,7 +19995,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -20009,7 +20015,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -20027,10 +20033,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121086197</v>
+        <v>121080224</v>
       </c>
       <c r="B143" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -20062,7 +20068,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>590</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20087,13 +20093,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500913</v>
+        <v>500615</v>
       </c>
       <c r="R143" t="n">
-        <v>7013871</v>
+        <v>7013796</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -20127,7 +20133,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -20147,7 +20153,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -20168,7 +20174,7 @@
         <v>121086141</v>
       </c>
       <c r="B144" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -20315,10 +20321,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121081815</v>
+        <v>121082256</v>
       </c>
       <c r="B145" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -20327,58 +20333,46 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500786</v>
+        <v>500776</v>
       </c>
       <c r="R145" t="n">
-        <v>7013863</v>
+        <v>7013871</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -20415,7 +20409,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -20424,7 +20418,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -20436,6 +20429,26 @@
       <c r="AI145" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -20453,10 +20466,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121080224</v>
+        <v>121085785</v>
       </c>
       <c r="B146" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -20488,7 +20501,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -20498,7 +20511,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -20513,13 +20526,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500615</v>
+        <v>500828</v>
       </c>
       <c r="R146" t="n">
-        <v>7013796</v>
+        <v>7013875</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -20553,7 +20566,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -20573,7 +20586,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -20591,10 +20604,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121081860</v>
+        <v>121086004</v>
       </c>
       <c r="B147" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -20603,41 +20616,58 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500786</v>
+        <v>500853</v>
       </c>
       <c r="R147" t="n">
-        <v>7013863</v>
+        <v>7013862</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -20674,7 +20704,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st. skott/stjälkar och 2 st. fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -20695,26 +20725,6 @@
       <c r="AI147" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -20732,10 +20742,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121082732</v>
+        <v>121081304</v>
       </c>
       <c r="B148" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -20744,41 +20754,58 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500776</v>
+        <v>500622</v>
       </c>
       <c r="R148" t="n">
-        <v>7013871</v>
+        <v>7013801</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -20815,7 +20842,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -20835,27 +20862,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -20873,10 +20880,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121082256</v>
+        <v>121082671</v>
       </c>
       <c r="B149" t="n">
-        <v>57351</v>
+        <v>98094</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -20885,36 +20892,48 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
@@ -20961,7 +20980,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 130 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -20970,6 +20989,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -20981,26 +21001,6 @@
       <c r="AI149" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -21018,10 +21018,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121196283</v>
+        <v>121201394</v>
       </c>
       <c r="B150" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500872</v>
+        <v>500242</v>
       </c>
       <c r="R150" t="n">
-        <v>7013820</v>
+        <v>7013801</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -21108,17 +21108,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21156,10 +21156,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121201394</v>
+        <v>121197538</v>
       </c>
       <c r="B151" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21201,7 +21201,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500242</v>
+        <v>500895</v>
       </c>
       <c r="R151" t="n">
-        <v>7013801</v>
+        <v>7013735</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -21246,17 +21246,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121201748</v>
+        <v>121195472</v>
       </c>
       <c r="B152" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21354,10 +21354,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500205</v>
+        <v>500883</v>
       </c>
       <c r="R152" t="n">
-        <v>7013878</v>
+        <v>7013806</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -21384,17 +21384,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -21432,10 +21432,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121196729</v>
+        <v>121203565</v>
       </c>
       <c r="B153" t="n">
-        <v>98081</v>
+        <v>98011</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -21444,30 +21444,30 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21481,24 +21481,20 @@
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500833</v>
+        <v>500210</v>
       </c>
       <c r="R153" t="n">
-        <v>7013748</v>
+        <v>7014055</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -21522,17 +21518,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21552,7 +21548,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21570,10 +21566,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121196381</v>
+        <v>121196283</v>
       </c>
       <c r="B154" t="n">
-        <v>79711</v>
+        <v>98094</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -21582,35 +21578,48 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
@@ -21657,7 +21666,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -21678,31 +21687,6 @@
       <c r="AI154" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -21720,10 +21704,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121197288</v>
+        <v>121196381</v>
       </c>
       <c r="B155" t="n">
-        <v>79682</v>
+        <v>79714</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -21732,32 +21716,32 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -21767,10 +21751,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500924</v>
+        <v>500872</v>
       </c>
       <c r="R155" t="n">
-        <v>7013754</v>
+        <v>7013820</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -21807,7 +21791,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -21827,7 +21811,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -21842,17 +21826,17 @@
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>En skadad död stående sälgstam.</t>
+          <t>En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -21870,10 +21854,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121196322</v>
+        <v>121201836</v>
       </c>
       <c r="B156" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21882,45 +21866,58 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500872</v>
+        <v>500162</v>
       </c>
       <c r="R156" t="n">
-        <v>7013820</v>
+        <v>7013924</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -21947,17 +21944,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -21977,35 +21974,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL156" t="inlineStr">
-        <is>
-          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN156" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -22023,10 +21992,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121203688</v>
+        <v>121196322</v>
       </c>
       <c r="B157" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -22035,61 +22004,48 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500200</v>
+        <v>500872</v>
       </c>
       <c r="R157" t="n">
-        <v>7014080</v>
+        <v>7013820</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -22113,17 +22069,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22143,7 +22099,35 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22161,10 +22145,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121201641</v>
+        <v>121201748</v>
       </c>
       <c r="B158" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -22196,7 +22180,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22221,10 +22205,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500241</v>
+        <v>500205</v>
       </c>
       <c r="R158" t="n">
-        <v>7013834</v>
+        <v>7013878</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -22261,7 +22245,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -22299,10 +22283,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121197538</v>
+        <v>121198065</v>
       </c>
       <c r="B159" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -22334,7 +22318,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -22344,7 +22328,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -22359,10 +22343,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500895</v>
+        <v>500857</v>
       </c>
       <c r="R159" t="n">
-        <v>7013735</v>
+        <v>7013723</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22399,7 +22383,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22437,10 +22421,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121195472</v>
+        <v>121196729</v>
       </c>
       <c r="B160" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -22472,7 +22456,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -22497,10 +22481,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500883</v>
+        <v>500833</v>
       </c>
       <c r="R160" t="n">
-        <v>7013806</v>
+        <v>7013748</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -22537,7 +22521,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22557,7 +22541,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -22575,10 +22559,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121198065</v>
+        <v>121203724</v>
       </c>
       <c r="B161" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -22610,7 +22594,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -22635,10 +22619,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>500857</v>
+        <v>500179</v>
       </c>
       <c r="R161" t="n">
-        <v>7013723</v>
+        <v>7013960</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -22665,17 +22649,17 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -22695,7 +22679,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -22713,10 +22697,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121201836</v>
+        <v>121201641</v>
       </c>
       <c r="B162" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -22748,7 +22732,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -22773,10 +22757,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>500162</v>
+        <v>500241</v>
       </c>
       <c r="R162" t="n">
-        <v>7013924</v>
+        <v>7013834</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -22813,7 +22797,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -22833,7 +22817,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -22851,10 +22835,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121203565</v>
+        <v>121203688</v>
       </c>
       <c r="B163" t="n">
-        <v>97998</v>
+        <v>98094</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -22863,30 +22847,30 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22900,17 +22884,21 @@
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500210</v>
+        <v>500200</v>
       </c>
       <c r="R163" t="n">
-        <v>7014055</v>
+        <v>7014080</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -22947,7 +22935,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22967,7 +22955,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22985,10 +22973,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121203724</v>
+        <v>121197288</v>
       </c>
       <c r="B164" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -22997,58 +22985,45 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500179</v>
+        <v>500924</v>
       </c>
       <c r="R164" t="n">
-        <v>7013960</v>
+        <v>7013754</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -23075,17 +23050,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23105,7 +23080,32 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318594</v>
+        <v>121318473</v>
       </c>
       <c r="B165" t="n">
-        <v>57504</v>
+        <v>90705</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,50 +23139,45 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R165" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -23228,6 +23223,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23238,7 +23234,27 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23256,7 +23272,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121318402</v>
+        <v>121318594</v>
       </c>
       <c r="B166" t="n">
         <v>57504</v>
@@ -23308,14 +23324,14 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R166" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -23371,7 +23387,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -23389,10 +23405,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318473</v>
+        <v>121318402</v>
       </c>
       <c r="B167" t="n">
-        <v>90693</v>
+        <v>57504</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23405,35 +23421,40 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23489,7 +23510,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -23501,26 +23521,6 @@
       <c r="AI167" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121339861</v>
+        <v>121335375</v>
       </c>
       <c r="B168" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,41 +23550,58 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500140</v>
+        <v>500170</v>
       </c>
       <c r="R168" t="n">
-        <v>7013999</v>
+        <v>7014032</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23621,7 +23638,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23641,32 +23658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL168" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23684,10 +23676,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339923</v>
+        <v>121339782</v>
       </c>
       <c r="B169" t="n">
-        <v>91380</v>
+        <v>98094</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23696,53 +23688,58 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500108</v>
+        <v>500152</v>
       </c>
       <c r="R169" t="n">
-        <v>7013909</v>
+        <v>7013957</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -23777,6 +23774,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -23794,27 +23796,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23832,10 +23814,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339744</v>
+        <v>121339956</v>
       </c>
       <c r="B170" t="n">
-        <v>90715</v>
+        <v>98094</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23844,56 +23826,61 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500169</v>
+        <v>500265</v>
       </c>
       <c r="R170" t="n">
-        <v>7013982</v>
+        <v>7013735</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -23927,7 +23914,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23947,27 +23934,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23985,10 +23952,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339897</v>
+        <v>121339542</v>
       </c>
       <c r="B171" t="n">
-        <v>98081</v>
+        <v>90727</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23997,61 +23964,56 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500163</v>
+        <v>500188</v>
       </c>
       <c r="R171" t="n">
-        <v>7013970</v>
+        <v>7013973</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24085,7 +24047,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24105,7 +24067,27 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24123,10 +24105,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121339956</v>
+        <v>121339744</v>
       </c>
       <c r="B172" t="n">
-        <v>98081</v>
+        <v>90727</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24135,61 +24117,56 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500265</v>
+        <v>500169</v>
       </c>
       <c r="R172" t="n">
-        <v>7013735</v>
+        <v>7013982</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -24223,7 +24200,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24243,7 +24220,27 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24261,10 +24258,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121335375</v>
+        <v>121335603</v>
       </c>
       <c r="B173" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24273,43 +24270,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N173" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24317,14 +24306,14 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500170</v>
+        <v>500182</v>
       </c>
       <c r="R173" t="n">
-        <v>7014032</v>
+        <v>7014067</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24361,7 +24350,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24370,7 +24359,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -24381,7 +24369,27 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24399,10 +24407,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121339782</v>
+        <v>121339897</v>
       </c>
       <c r="B174" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24434,7 +24442,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -24455,14 +24463,14 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500152</v>
+        <v>500163</v>
       </c>
       <c r="R174" t="n">
-        <v>7013957</v>
+        <v>7013970</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -24499,7 +24507,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24519,7 +24527,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24537,10 +24545,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121339542</v>
+        <v>121339038</v>
       </c>
       <c r="B175" t="n">
-        <v>90715</v>
+        <v>98094</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24549,56 +24557,61 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500188</v>
+        <v>500173</v>
       </c>
       <c r="R175" t="n">
-        <v>7013973</v>
+        <v>7014080</v>
       </c>
       <c r="S175" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -24632,7 +24645,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24652,27 +24665,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24690,10 +24683,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339891</v>
+        <v>121338927</v>
       </c>
       <c r="B176" t="n">
-        <v>57351</v>
+        <v>98011</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24702,35 +24695,43 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24738,17 +24739,17 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500163</v>
+        <v>500220</v>
       </c>
       <c r="R176" t="n">
-        <v>7013970</v>
+        <v>7014127</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -24782,7 +24783,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24791,6 +24792,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -24801,27 +24803,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24839,10 +24821,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121335603</v>
+        <v>121338977</v>
       </c>
       <c r="B177" t="n">
-        <v>57351</v>
+        <v>98094</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24851,35 +24833,43 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24887,17 +24877,17 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500182</v>
+        <v>500191</v>
       </c>
       <c r="R177" t="n">
-        <v>7014067</v>
+        <v>7014126</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24931,7 +24921,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24940,6 +24930,7 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -24950,27 +24941,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24988,10 +24959,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121337877</v>
+        <v>121339476</v>
       </c>
       <c r="B178" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -25023,7 +24994,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -25048,13 +25019,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500184</v>
+        <v>500200</v>
       </c>
       <c r="R178" t="n">
-        <v>7014123</v>
+        <v>7014028</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -25088,7 +25059,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25108,7 +25079,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25126,10 +25097,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121339649</v>
+        <v>121340000</v>
       </c>
       <c r="B179" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25138,61 +25109,48 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500207</v>
+        <v>500299</v>
       </c>
       <c r="R179" t="n">
-        <v>7013937</v>
+        <v>7013696</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -25226,7 +25184,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25246,7 +25204,27 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25264,10 +25242,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121340000</v>
+        <v>121339923</v>
       </c>
       <c r="B180" t="n">
-        <v>90697</v>
+        <v>91392</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25276,29 +25254,37 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -25311,13 +25297,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500299</v>
+        <v>500108</v>
       </c>
       <c r="R180" t="n">
-        <v>7013696</v>
+        <v>7013909</v>
       </c>
       <c r="S180" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -25347,11 +25333,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25386,12 +25367,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25409,10 +25390,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121338977</v>
+        <v>121337877</v>
       </c>
       <c r="B181" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25444,7 +25425,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -25454,7 +25435,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -25469,10 +25450,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500191</v>
+        <v>500184</v>
       </c>
       <c r="R181" t="n">
-        <v>7014126</v>
+        <v>7014123</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25509,7 +25490,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25547,10 +25528,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339991</v>
+        <v>121339861</v>
       </c>
       <c r="B182" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25563,21 +25544,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -25590,10 +25571,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500281</v>
+        <v>500140</v>
       </c>
       <c r="R182" t="n">
-        <v>7013721</v>
+        <v>7013999</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -25630,7 +25611,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25663,14 +25644,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25688,10 +25674,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121338927</v>
+        <v>121339891</v>
       </c>
       <c r="B183" t="n">
-        <v>97998</v>
+        <v>57351</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25700,43 +25686,35 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N183" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25744,17 +25722,17 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500220</v>
+        <v>500163</v>
       </c>
       <c r="R183" t="n">
-        <v>7014127</v>
+        <v>7013970</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -25788,7 +25766,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25797,7 +25775,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -25808,7 +25785,27 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25826,10 +25823,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339476</v>
+        <v>121339649</v>
       </c>
       <c r="B184" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25861,7 +25858,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25871,7 +25868,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -25886,10 +25883,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500200</v>
+        <v>500207</v>
       </c>
       <c r="R184" t="n">
-        <v>7014028</v>
+        <v>7013937</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -25926,7 +25923,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25964,10 +25961,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339038</v>
+        <v>121339991</v>
       </c>
       <c r="B185" t="n">
-        <v>98081</v>
+        <v>90727</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25976,58 +25973,41 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500173</v>
+        <v>500281</v>
       </c>
       <c r="R185" t="n">
-        <v>7014080</v>
+        <v>7013721</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -26064,7 +26044,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26064,27 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -18781,10 +18781,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121086682</v>
+        <v>121081860</v>
       </c>
       <c r="B134" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -18793,58 +18793,41 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500914</v>
+        <v>500786</v>
       </c>
       <c r="R134" t="n">
-        <v>7013834</v>
+        <v>7013863</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -18881,7 +18864,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -18901,7 +18884,27 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -18919,10 +18922,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121081815</v>
+        <v>121082732</v>
       </c>
       <c r="B135" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -18931,58 +18934,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500786</v>
+        <v>500776</v>
       </c>
       <c r="R135" t="n">
-        <v>7013863</v>
+        <v>7013871</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -19019,7 +19005,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -19040,6 +19026,26 @@
       <c r="AI135" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -19057,10 +19063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121086197</v>
+        <v>121080224</v>
       </c>
       <c r="B136" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -19092,7 +19098,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>590</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19117,13 +19123,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>500913</v>
+        <v>500615</v>
       </c>
       <c r="R136" t="n">
-        <v>7013871</v>
+        <v>7013796</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -19157,7 +19163,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19177,7 +19183,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -19195,10 +19201,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121081560</v>
+        <v>121082256</v>
       </c>
       <c r="B137" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -19211,37 +19217,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>500739</v>
+        <v>500776</v>
       </c>
       <c r="R137" t="n">
-        <v>7013841</v>
+        <v>7013871</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -19278,7 +19289,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -19287,7 +19298,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -19313,12 +19323,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -19336,10 +19346,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121081765</v>
+        <v>121081815</v>
       </c>
       <c r="B138" t="n">
-        <v>57504</v>
+        <v>98095</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -19348,25 +19358,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -19374,13 +19384,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N138" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19432,7 +19446,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st skott/stjälk inom ca 0,5 m2 yta vid en död tall med full längd. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -19441,6 +19455,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -19469,10 +19484,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121082022</v>
+        <v>121086197</v>
       </c>
       <c r="B139" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -19481,35 +19496,43 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19517,14 +19540,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>500784</v>
+        <v>500913</v>
       </c>
       <c r="R139" t="n">
-        <v>7013868</v>
+        <v>7013871</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -19561,7 +19584,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st. skott/stjälkar och 1 st. fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -19570,6 +19593,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -19580,22 +19604,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på fuktig- och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -19613,7 +19622,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121081860</v>
+        <v>121081560</v>
       </c>
       <c r="B140" t="n">
         <v>78604</v>
@@ -19652,14 +19661,14 @@
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>500786</v>
+        <v>500739</v>
       </c>
       <c r="R140" t="n">
-        <v>7013863</v>
+        <v>7013841</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -19754,10 +19763,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121082732</v>
+        <v>121086141</v>
       </c>
       <c r="B141" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -19770,37 +19779,41 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>500776</v>
+        <v>500882</v>
       </c>
       <c r="R141" t="n">
-        <v>7013871</v>
+        <v>7013873</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -19837,7 +19850,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -19857,27 +19870,32 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -19895,10 +19913,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121086728</v>
+        <v>121081765</v>
       </c>
       <c r="B142" t="n">
-        <v>98094</v>
+        <v>57504</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -19907,25 +19925,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -19933,17 +19951,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19951,14 +19965,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>500895</v>
+        <v>500786</v>
       </c>
       <c r="R142" t="n">
-        <v>7013833</v>
+        <v>7013863</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -19995,7 +20009,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -20004,7 +20018,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -20015,7 +20028,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -20033,10 +20046,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121080224</v>
+        <v>121086004</v>
       </c>
       <c r="B143" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -20068,7 +20081,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20093,13 +20106,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>500615</v>
+        <v>500853</v>
       </c>
       <c r="R143" t="n">
-        <v>7013796</v>
+        <v>7013862</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -20133,7 +20146,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Knärot med minst 590 st skott/stjälkar och 7 st fröställningar fläckvis och bitvis mattbildande inom ca 10 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st. skott/stjälkar och 2 st. fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -20153,7 +20166,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -20171,10 +20184,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121086141</v>
+        <v>121086728</v>
       </c>
       <c r="B144" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -20183,45 +20196,58 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>500882</v>
+        <v>500895</v>
       </c>
       <c r="R144" t="n">
-        <v>7013873</v>
+        <v>7013833</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -20258,7 +20284,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 1 st. skott/stjälk med fröställning. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -20279,31 +20305,6 @@
       <c r="AI144" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad böjd sälg med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -20321,10 +20322,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121082256</v>
+        <v>121085785</v>
       </c>
       <c r="B145" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -20333,46 +20334,58 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>500776</v>
+        <v>500828</v>
       </c>
       <c r="R145" t="n">
-        <v>7013871</v>
+        <v>7013875</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -20409,7 +20422,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack-spår längs ett par meter av en granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -20418,6 +20431,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -20429,26 +20443,6 @@
       <c r="AI145" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -20466,10 +20460,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121085785</v>
+        <v>121081304</v>
       </c>
       <c r="B146" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -20501,7 +20495,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -20526,10 +20520,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>500828</v>
+        <v>500622</v>
       </c>
       <c r="R146" t="n">
-        <v>7013875</v>
+        <v>7013801</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -20566,7 +20560,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Knärot med minst 93 st skott/stjälkar inom ca 1 m2 yta intill en hyfsat grov tall. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -20586,7 +20580,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -20604,10 +20598,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121086004</v>
+        <v>121082022</v>
       </c>
       <c r="B147" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -20616,43 +20610,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -20660,14 +20646,14 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Fjälån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>500853</v>
+        <v>500784</v>
       </c>
       <c r="R147" t="n">
-        <v>7013862</v>
+        <v>7013868</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -20704,7 +20690,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st. skott/stjälkar och 2 st. fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack-spår på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -20713,7 +20699,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -20725,6 +20710,21 @@
       <c r="AI147" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -20742,10 +20742,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121081304</v>
+        <v>121086682</v>
       </c>
       <c r="B148" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>500622</v>
+        <v>500914</v>
       </c>
       <c r="R148" t="n">
-        <v>7013801</v>
+        <v>7013834</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 100 st. skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -20883,7 +20883,7 @@
         <v>121082671</v>
       </c>
       <c r="B149" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -21018,10 +21018,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121201394</v>
+        <v>121203565</v>
       </c>
       <c r="B150" t="n">
-        <v>98094</v>
+        <v>98012</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -21030,30 +21030,30 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21067,24 +21067,20 @@
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500242</v>
+        <v>500210</v>
       </c>
       <c r="R150" t="n">
-        <v>7013801</v>
+        <v>7014055</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -21118,7 +21114,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21138,7 +21134,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21156,10 +21152,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121197538</v>
+        <v>121196322</v>
       </c>
       <c r="B151" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -21168,58 +21164,45 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500895</v>
+        <v>500872</v>
       </c>
       <c r="R151" t="n">
-        <v>7013735</v>
+        <v>7013820</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -21256,7 +21239,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21276,7 +21259,35 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -21294,10 +21305,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121195472</v>
+        <v>121201836</v>
       </c>
       <c r="B152" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21329,7 +21340,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21354,10 +21365,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500883</v>
+        <v>500162</v>
       </c>
       <c r="R152" t="n">
-        <v>7013806</v>
+        <v>7013924</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -21384,17 +21395,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21414,7 +21425,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -21432,10 +21443,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121203565</v>
+        <v>121201748</v>
       </c>
       <c r="B153" t="n">
-        <v>98011</v>
+        <v>98095</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -21444,30 +21455,30 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21481,20 +21492,24 @@
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500210</v>
+        <v>500205</v>
       </c>
       <c r="R153" t="n">
-        <v>7014055</v>
+        <v>7013878</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -21528,7 +21543,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21548,7 +21563,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21566,10 +21581,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121196283</v>
+        <v>121203724</v>
       </c>
       <c r="B154" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -21601,7 +21616,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -21626,10 +21641,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500872</v>
+        <v>500179</v>
       </c>
       <c r="R154" t="n">
-        <v>7013820</v>
+        <v>7013960</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -21656,17 +21671,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -21686,7 +21701,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -21704,10 +21719,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121196381</v>
+        <v>121195472</v>
       </c>
       <c r="B155" t="n">
-        <v>79714</v>
+        <v>98095</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -21716,45 +21731,58 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500872</v>
+        <v>500883</v>
       </c>
       <c r="R155" t="n">
-        <v>7013820</v>
+        <v>7013806</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -21791,7 +21819,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -21811,32 +21839,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL155" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -21854,10 +21857,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121201836</v>
+        <v>121197288</v>
       </c>
       <c r="B156" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21866,58 +21869,45 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500162</v>
+        <v>500924</v>
       </c>
       <c r="R156" t="n">
-        <v>7013924</v>
+        <v>7013754</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -21944,17 +21934,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -21974,7 +21964,32 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -21992,10 +22007,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121196322</v>
+        <v>121196381</v>
       </c>
       <c r="B157" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -22004,32 +22019,32 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -22079,7 +22094,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22099,7 +22114,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -22114,7 +22129,7 @@
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -22122,12 +22137,9 @@
           <t>Bark på levande träd</t>
         </is>
       </c>
-      <c r="AN157" t="n">
-        <v>2</v>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22145,10 +22157,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121201748</v>
+        <v>121196283</v>
       </c>
       <c r="B158" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -22180,7 +22192,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22205,10 +22217,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500205</v>
+        <v>500872</v>
       </c>
       <c r="R158" t="n">
-        <v>7013878</v>
+        <v>7013820</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -22235,17 +22247,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -22265,7 +22277,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -22283,10 +22295,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121198065</v>
+        <v>121196729</v>
       </c>
       <c r="B159" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -22318,7 +22330,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -22343,10 +22355,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500857</v>
+        <v>500833</v>
       </c>
       <c r="R159" t="n">
-        <v>7013723</v>
+        <v>7013748</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22383,7 +22395,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22403,7 +22415,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -22421,10 +22433,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121196729</v>
+        <v>121197538</v>
       </c>
       <c r="B160" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -22456,7 +22468,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -22466,7 +22478,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -22481,10 +22493,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500833</v>
+        <v>500895</v>
       </c>
       <c r="R160" t="n">
-        <v>7013748</v>
+        <v>7013735</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -22521,7 +22533,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22541,7 +22553,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -22559,10 +22571,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121203724</v>
+        <v>121201641</v>
       </c>
       <c r="B161" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -22594,7 +22606,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -22619,10 +22631,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>500179</v>
+        <v>500241</v>
       </c>
       <c r="R161" t="n">
-        <v>7013960</v>
+        <v>7013834</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -22659,7 +22671,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -22679,7 +22691,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -22697,10 +22709,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121201641</v>
+        <v>121203688</v>
       </c>
       <c r="B162" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -22732,7 +22744,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -22757,13 +22769,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>500241</v>
+        <v>500200</v>
       </c>
       <c r="R162" t="n">
-        <v>7013834</v>
+        <v>7014080</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -22797,7 +22809,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -22817,7 +22829,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -22835,10 +22847,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121203688</v>
+        <v>121201394</v>
       </c>
       <c r="B163" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -22870,7 +22882,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22895,13 +22907,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500200</v>
+        <v>500242</v>
       </c>
       <c r="R163" t="n">
-        <v>7014080</v>
+        <v>7013801</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -22935,7 +22947,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22955,7 +22967,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22973,10 +22985,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121197288</v>
+        <v>121198065</v>
       </c>
       <c r="B164" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -22985,45 +22997,58 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500924</v>
+        <v>500857</v>
       </c>
       <c r="R164" t="n">
-        <v>7013754</v>
+        <v>7013723</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -23060,7 +23085,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23080,32 +23105,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>En skadad död stående sälgstam.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318473</v>
+        <v>121318402</v>
       </c>
       <c r="B165" t="n">
-        <v>90705</v>
+        <v>57504</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,35 +23139,40 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23223,7 +23228,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23235,26 +23239,6 @@
       <c r="AI165" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23272,10 +23256,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121318594</v>
+        <v>121318473</v>
       </c>
       <c r="B166" t="n">
-        <v>57504</v>
+        <v>90706</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -23288,50 +23272,45 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R166" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -23377,6 +23356,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -23387,7 +23367,27 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318402</v>
+        <v>121318594</v>
       </c>
       <c r="B167" t="n">
         <v>57504</v>
@@ -23457,14 +23457,14 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R167" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121335375</v>
+        <v>121339991</v>
       </c>
       <c r="B168" t="n">
-        <v>98094</v>
+        <v>90728</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,58 +23550,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500170</v>
+        <v>500281</v>
       </c>
       <c r="R168" t="n">
-        <v>7014032</v>
+        <v>7013721</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23638,7 +23621,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23658,7 +23641,27 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23676,10 +23679,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339782</v>
+        <v>121339891</v>
       </c>
       <c r="B169" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23688,43 +23691,35 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -23732,14 +23727,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500152</v>
+        <v>500163</v>
       </c>
       <c r="R169" t="n">
-        <v>7013957</v>
+        <v>7013970</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -23776,7 +23771,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23785,7 +23780,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -23796,7 +23790,27 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23814,10 +23828,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339956</v>
+        <v>121339744</v>
       </c>
       <c r="B170" t="n">
-        <v>98094</v>
+        <v>90728</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23826,61 +23840,56 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500265</v>
+        <v>500169</v>
       </c>
       <c r="R170" t="n">
-        <v>7013735</v>
+        <v>7013982</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -23914,7 +23923,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23934,7 +23943,27 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23952,10 +23981,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339542</v>
+        <v>121339861</v>
       </c>
       <c r="B171" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23968,38 +23997,26 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -24007,13 +24024,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500188</v>
+        <v>500140</v>
       </c>
       <c r="R171" t="n">
-        <v>7013973</v>
+        <v>7013999</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24047,7 +24064,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24067,7 +24084,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ171" t="inlineStr">
@@ -24080,14 +24097,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24105,10 +24127,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121339744</v>
+        <v>121339542</v>
       </c>
       <c r="B172" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24140,7 +24162,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -24160,13 +24182,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500169</v>
+        <v>500188</v>
       </c>
       <c r="R172" t="n">
-        <v>7013982</v>
+        <v>7013973</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -24200,7 +24222,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24220,7 +24242,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -24235,12 +24257,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24258,10 +24280,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121335603</v>
+        <v>121339923</v>
       </c>
       <c r="B173" t="n">
-        <v>57351</v>
+        <v>91393</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24270,50 +24292,53 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500182</v>
+        <v>500108</v>
       </c>
       <c r="R173" t="n">
-        <v>7014067</v>
+        <v>7013909</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24348,17 +24373,13 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -24369,7 +24390,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
@@ -24384,12 +24405,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24407,10 +24428,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121339897</v>
+        <v>121339649</v>
       </c>
       <c r="B174" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24442,7 +24463,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -24452,7 +24473,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
@@ -24463,14 +24484,14 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500163</v>
+        <v>500207</v>
       </c>
       <c r="R174" t="n">
-        <v>7013970</v>
+        <v>7013937</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -24507,7 +24528,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24527,7 +24548,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24548,7 +24569,7 @@
         <v>121339038</v>
       </c>
       <c r="B175" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24683,10 +24704,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121338927</v>
+        <v>121339956</v>
       </c>
       <c r="B176" t="n">
-        <v>98011</v>
+        <v>98095</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24695,30 +24716,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -24743,10 +24764,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500220</v>
+        <v>500265</v>
       </c>
       <c r="R176" t="n">
-        <v>7014127</v>
+        <v>7013735</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -24783,7 +24804,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24803,7 +24824,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24821,10 +24842,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121338977</v>
+        <v>121339782</v>
       </c>
       <c r="B177" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24856,7 +24877,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -24866,7 +24887,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -24881,13 +24902,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500191</v>
+        <v>500152</v>
       </c>
       <c r="R177" t="n">
-        <v>7014126</v>
+        <v>7013957</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24921,7 +24942,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24941,7 +24962,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24959,10 +24980,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121339476</v>
+        <v>121338977</v>
       </c>
       <c r="B178" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -24994,7 +25015,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -25004,7 +25025,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -25019,13 +25040,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500200</v>
+        <v>500191</v>
       </c>
       <c r="R178" t="n">
-        <v>7014028</v>
+        <v>7014126</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -25059,7 +25080,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25079,7 +25100,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25097,10 +25118,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121340000</v>
+        <v>121335375</v>
       </c>
       <c r="B179" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25109,48 +25130,61 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500299</v>
+        <v>500170</v>
       </c>
       <c r="R179" t="n">
-        <v>7013696</v>
+        <v>7014032</v>
       </c>
       <c r="S179" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -25184,7 +25218,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25204,27 +25238,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25242,10 +25256,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121339923</v>
+        <v>121338927</v>
       </c>
       <c r="B180" t="n">
-        <v>91392</v>
+        <v>98012</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25258,52 +25272,57 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3298</v>
+        <v>219790</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500108</v>
+        <v>500220</v>
       </c>
       <c r="R180" t="n">
-        <v>7013909</v>
+        <v>7014127</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -25333,6 +25352,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25352,27 +25376,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25390,10 +25394,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121337877</v>
+        <v>121340000</v>
       </c>
       <c r="B181" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25402,58 +25406,45 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500184</v>
+        <v>500299</v>
       </c>
       <c r="R181" t="n">
-        <v>7014123</v>
+        <v>7013696</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25490,7 +25481,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25510,7 +25501,27 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25528,10 +25539,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339861</v>
+        <v>121339897</v>
       </c>
       <c r="B182" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25540,41 +25551,58 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500140</v>
+        <v>500163</v>
       </c>
       <c r="R182" t="n">
-        <v>7013999</v>
+        <v>7013970</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -25611,7 +25639,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25632,31 +25660,6 @@
       <c r="AI182" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL182" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25674,10 +25677,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339891</v>
+        <v>121339476</v>
       </c>
       <c r="B183" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25686,35 +25689,43 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N183" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25722,14 +25733,14 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500163</v>
+        <v>500200</v>
       </c>
       <c r="R183" t="n">
-        <v>7013970</v>
+        <v>7014028</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -25766,7 +25777,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25775,6 +25786,7 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -25785,27 +25797,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25823,10 +25815,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339649</v>
+        <v>121335603</v>
       </c>
       <c r="B184" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25835,43 +25827,35 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25879,14 +25863,14 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500207</v>
+        <v>500182</v>
       </c>
       <c r="R184" t="n">
-        <v>7013937</v>
+        <v>7014067</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -25923,7 +25907,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25932,7 +25916,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -25943,7 +25926,27 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25961,10 +25964,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339991</v>
+        <v>121337877</v>
       </c>
       <c r="B185" t="n">
-        <v>90727</v>
+        <v>98095</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25973,44 +25976,61 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500281</v>
+        <v>500184</v>
       </c>
       <c r="R185" t="n">
-        <v>7013721</v>
+        <v>7014123</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26044,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26064,27 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -21018,10 +21018,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121203565</v>
+        <v>121196729</v>
       </c>
       <c r="B150" t="n">
-        <v>98012</v>
+        <v>98098</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -21030,30 +21030,30 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21067,20 +21067,24 @@
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500210</v>
+        <v>500833</v>
       </c>
       <c r="R150" t="n">
-        <v>7014055</v>
+        <v>7013748</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -21104,17 +21108,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21134,7 +21138,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21152,10 +21156,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121196322</v>
+        <v>121197538</v>
       </c>
       <c r="B151" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -21164,45 +21168,58 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500872</v>
+        <v>500895</v>
       </c>
       <c r="R151" t="n">
-        <v>7013820</v>
+        <v>7013735</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -21239,7 +21256,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21259,35 +21276,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL151" t="inlineStr">
-        <is>
-          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -21305,10 +21294,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121201836</v>
+        <v>121197288</v>
       </c>
       <c r="B152" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21317,58 +21306,45 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500162</v>
+        <v>500924</v>
       </c>
       <c r="R152" t="n">
-        <v>7013924</v>
+        <v>7013754</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -21395,17 +21371,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21425,7 +21401,32 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -21443,10 +21444,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121201748</v>
+        <v>121201641</v>
       </c>
       <c r="B153" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -21478,7 +21479,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21503,10 +21504,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500205</v>
+        <v>500241</v>
       </c>
       <c r="R153" t="n">
-        <v>7013878</v>
+        <v>7013834</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -21543,7 +21544,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21584,7 +21585,7 @@
         <v>121203724</v>
       </c>
       <c r="B154" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -21719,10 +21720,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121195472</v>
+        <v>121201394</v>
       </c>
       <c r="B155" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -21754,7 +21755,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -21779,10 +21780,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500883</v>
+        <v>500242</v>
       </c>
       <c r="R155" t="n">
-        <v>7013806</v>
+        <v>7013801</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -21809,17 +21810,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -21839,7 +21840,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -21857,10 +21858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121197288</v>
+        <v>121203565</v>
       </c>
       <c r="B156" t="n">
-        <v>79685</v>
+        <v>98015</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21869,34 +21870,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -21904,13 +21914,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500924</v>
+        <v>500210</v>
       </c>
       <c r="R156" t="n">
-        <v>7013754</v>
+        <v>7014055</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -21934,17 +21944,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -21964,32 +21974,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL156" t="inlineStr">
-        <is>
-          <t>En skadad död stående sälgstam.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -22007,10 +21992,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121196381</v>
+        <v>121196283</v>
       </c>
       <c r="B157" t="n">
-        <v>79714</v>
+        <v>98098</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -22019,35 +22004,48 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
@@ -22094,7 +22092,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22115,31 +22113,6 @@
       <c r="AI157" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL157" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22157,10 +22130,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121196283</v>
+        <v>121198065</v>
       </c>
       <c r="B158" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -22192,7 +22165,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22217,10 +22190,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500872</v>
+        <v>500857</v>
       </c>
       <c r="R158" t="n">
-        <v>7013820</v>
+        <v>7013723</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -22257,7 +22230,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -22277,7 +22250,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -22295,10 +22268,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121196729</v>
+        <v>121196381</v>
       </c>
       <c r="B159" t="n">
-        <v>98095</v>
+        <v>79717</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -22307,58 +22280,45 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500833</v>
+        <v>500872</v>
       </c>
       <c r="R159" t="n">
-        <v>7013748</v>
+        <v>7013820</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22395,7 +22355,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22415,7 +22375,32 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>En lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -22433,10 +22418,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121197538</v>
+        <v>121201836</v>
       </c>
       <c r="B160" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -22468,7 +22453,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -22478,7 +22463,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -22493,10 +22478,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500895</v>
+        <v>500162</v>
       </c>
       <c r="R160" t="n">
-        <v>7013735</v>
+        <v>7013924</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -22523,17 +22508,17 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22553,7 +22538,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -22571,10 +22556,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121201641</v>
+        <v>121196322</v>
       </c>
       <c r="B161" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -22583,58 +22568,45 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>500241</v>
+        <v>500872</v>
       </c>
       <c r="R161" t="n">
-        <v>7013834</v>
+        <v>7013820</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -22661,17 +22633,17 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -22691,7 +22663,35 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -22712,7 +22712,7 @@
         <v>121203688</v>
       </c>
       <c r="B162" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -22847,10 +22847,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121201394</v>
+        <v>121195472</v>
       </c>
       <c r="B163" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22907,10 +22907,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500242</v>
+        <v>500883</v>
       </c>
       <c r="R163" t="n">
-        <v>7013801</v>
+        <v>7013806</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -22937,17 +22937,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22985,10 +22985,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121198065</v>
+        <v>121201748</v>
       </c>
       <c r="B164" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -23045,10 +23045,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500857</v>
+        <v>500205</v>
       </c>
       <c r="R164" t="n">
-        <v>7013723</v>
+        <v>7013878</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -23075,17 +23075,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318402</v>
+        <v>121318473</v>
       </c>
       <c r="B165" t="n">
-        <v>57504</v>
+        <v>90709</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,40 +23139,35 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23228,6 +23223,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23239,6 +23235,26 @@
       <c r="AI165" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23256,10 +23272,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121318473</v>
+        <v>121318594</v>
       </c>
       <c r="B166" t="n">
-        <v>90706</v>
+        <v>57507</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -23272,45 +23288,50 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R166" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -23356,7 +23377,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -23367,27 +23387,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -23405,10 +23405,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318594</v>
+        <v>121318402</v>
       </c>
       <c r="B167" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23457,14 +23457,14 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R167" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121339991</v>
+        <v>121339923</v>
       </c>
       <c r="B168" t="n">
-        <v>90728</v>
+        <v>91396</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,30 +23550,42 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -23581,10 +23593,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500281</v>
+        <v>500108</v>
       </c>
       <c r="R168" t="n">
-        <v>7013721</v>
+        <v>7013909</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23619,11 +23631,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -23656,12 +23663,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23679,10 +23686,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339891</v>
+        <v>121339649</v>
       </c>
       <c r="B169" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23691,35 +23698,43 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -23727,14 +23742,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500163</v>
+        <v>500207</v>
       </c>
       <c r="R169" t="n">
-        <v>7013970</v>
+        <v>7013937</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -23771,7 +23786,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23780,6 +23795,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -23790,27 +23806,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23828,10 +23824,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339744</v>
+        <v>121339476</v>
       </c>
       <c r="B170" t="n">
-        <v>90728</v>
+        <v>98098</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23840,53 +23836,58 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500169</v>
+        <v>500200</v>
       </c>
       <c r="R170" t="n">
-        <v>7013982</v>
+        <v>7014028</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -23923,7 +23924,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23943,27 +23944,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23981,10 +23962,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339861</v>
+        <v>121339782</v>
       </c>
       <c r="B171" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23993,41 +23974,58 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500140</v>
+        <v>500152</v>
       </c>
       <c r="R171" t="n">
-        <v>7013999</v>
+        <v>7013957</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -24064,7 +24062,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24084,32 +24082,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL171" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24127,10 +24100,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121339542</v>
+        <v>121339891</v>
       </c>
       <c r="B172" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24143,52 +24116,49 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500188</v>
+        <v>500163</v>
       </c>
       <c r="R172" t="n">
-        <v>7013973</v>
+        <v>7013970</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -24222,7 +24192,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24231,7 +24201,6 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -24242,7 +24211,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -24257,12 +24226,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24280,10 +24249,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121339923</v>
+        <v>121339861</v>
       </c>
       <c r="B173" t="n">
-        <v>91393</v>
+        <v>78607</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24292,42 +24261,30 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
@@ -24335,10 +24292,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500108</v>
+        <v>500140</v>
       </c>
       <c r="R173" t="n">
-        <v>7013909</v>
+        <v>7013999</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24373,6 +24330,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -24403,14 +24365,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24428,10 +24395,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121339649</v>
+        <v>121335375</v>
       </c>
       <c r="B174" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24463,7 +24430,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -24473,7 +24440,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
@@ -24488,10 +24455,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500207</v>
+        <v>500170</v>
       </c>
       <c r="R174" t="n">
-        <v>7013937</v>
+        <v>7014032</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -24528,7 +24495,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24548,7 +24515,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24566,10 +24533,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121339038</v>
+        <v>121338927</v>
       </c>
       <c r="B175" t="n">
-        <v>98095</v>
+        <v>98015</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24578,30 +24545,30 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -24626,13 +24593,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500173</v>
+        <v>500220</v>
       </c>
       <c r="R175" t="n">
-        <v>7014080</v>
+        <v>7014127</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -24666,7 +24633,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24686,7 +24653,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24704,10 +24671,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339956</v>
+        <v>121339991</v>
       </c>
       <c r="B176" t="n">
-        <v>98095</v>
+        <v>90731</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24716,61 +24683,44 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500265</v>
+        <v>500281</v>
       </c>
       <c r="R176" t="n">
-        <v>7013735</v>
+        <v>7013721</v>
       </c>
       <c r="S176" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -24804,7 +24754,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24825,6 +24775,26 @@
       <c r="AI176" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24842,10 +24812,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121339782</v>
+        <v>121337877</v>
       </c>
       <c r="B177" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24877,7 +24847,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -24902,13 +24872,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500152</v>
+        <v>500184</v>
       </c>
       <c r="R177" t="n">
-        <v>7013957</v>
+        <v>7014123</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24942,7 +24912,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24962,7 +24932,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24983,7 +24953,7 @@
         <v>121338977</v>
       </c>
       <c r="B178" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -25118,10 +25088,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121335375</v>
+        <v>121339542</v>
       </c>
       <c r="B179" t="n">
-        <v>98095</v>
+        <v>90731</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25130,61 +25100,56 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500170</v>
+        <v>500188</v>
       </c>
       <c r="R179" t="n">
-        <v>7014032</v>
+        <v>7013973</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -25218,7 +25183,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25238,7 +25203,27 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25256,10 +25241,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121338927</v>
+        <v>121335603</v>
       </c>
       <c r="B180" t="n">
-        <v>98012</v>
+        <v>57354</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25268,43 +25253,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N180" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25312,17 +25289,17 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500220</v>
+        <v>500182</v>
       </c>
       <c r="R180" t="n">
-        <v>7014127</v>
+        <v>7014067</v>
       </c>
       <c r="S180" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -25356,7 +25333,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25365,7 +25342,6 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -25376,7 +25352,27 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25397,7 +25393,7 @@
         <v>121340000</v>
       </c>
       <c r="B181" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25542,7 +25538,7 @@
         <v>121339897</v>
       </c>
       <c r="B182" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25677,10 +25673,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339476</v>
+        <v>121339956</v>
       </c>
       <c r="B183" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25712,7 +25708,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -25737,13 +25733,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500200</v>
+        <v>500265</v>
       </c>
       <c r="R183" t="n">
-        <v>7014028</v>
+        <v>7013735</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -25777,7 +25773,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25797,7 +25793,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25815,10 +25811,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121335603</v>
+        <v>121339744</v>
       </c>
       <c r="B184" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25831,46 +25827,49 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500182</v>
+        <v>500169</v>
       </c>
       <c r="R184" t="n">
-        <v>7014067</v>
+        <v>7013982</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -25907,7 +25906,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25916,6 +25915,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
@@ -25941,12 +25941,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25964,10 +25964,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121337877</v>
+        <v>121339038</v>
       </c>
       <c r="B185" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -26024,13 +26024,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500184</v>
+        <v>500173</v>
       </c>
       <c r="R185" t="n">
-        <v>7014123</v>
+        <v>7014080</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -21018,7 +21018,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121196729</v>
+        <v>121196283</v>
       </c>
       <c r="B150" t="n">
         <v>98098</v>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500833</v>
+        <v>500872</v>
       </c>
       <c r="R150" t="n">
-        <v>7013748</v>
+        <v>7013820</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21156,7 +21156,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121197538</v>
+        <v>121198065</v>
       </c>
       <c r="B151" t="n">
         <v>98098</v>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21201,7 +21201,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500895</v>
+        <v>500857</v>
       </c>
       <c r="R151" t="n">
-        <v>7013735</v>
+        <v>7013723</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21294,10 +21294,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121197288</v>
+        <v>121203688</v>
       </c>
       <c r="B152" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21306,48 +21306,61 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500924</v>
+        <v>500200</v>
       </c>
       <c r="R152" t="n">
-        <v>7013754</v>
+        <v>7014080</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -21371,17 +21384,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21401,32 +21414,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL152" t="inlineStr">
-        <is>
-          <t>En skadad död stående sälgstam.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -21444,7 +21432,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121201641</v>
+        <v>121197538</v>
       </c>
       <c r="B153" t="n">
         <v>98098</v>
@@ -21479,7 +21467,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21489,7 +21477,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -21504,10 +21492,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500241</v>
+        <v>500895</v>
       </c>
       <c r="R153" t="n">
-        <v>7013834</v>
+        <v>7013735</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -21534,17 +21522,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21564,7 +21552,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21582,7 +21570,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121203724</v>
+        <v>121201641</v>
       </c>
       <c r="B154" t="n">
         <v>98098</v>
@@ -21617,7 +21605,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -21642,10 +21630,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500179</v>
+        <v>500241</v>
       </c>
       <c r="R154" t="n">
-        <v>7013960</v>
+        <v>7013834</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -21682,7 +21670,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -21702,7 +21690,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -21992,10 +21980,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121196283</v>
+        <v>121196381</v>
       </c>
       <c r="B157" t="n">
-        <v>98098</v>
+        <v>79717</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -22004,48 +21992,35 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
@@ -22092,7 +22067,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22113,6 +22088,31 @@
       <c r="AI157" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>En lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22130,7 +22130,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121198065</v>
+        <v>121201748</v>
       </c>
       <c r="B158" t="n">
         <v>98098</v>
@@ -22165,7 +22165,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22190,10 +22190,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500857</v>
+        <v>500205</v>
       </c>
       <c r="R158" t="n">
-        <v>7013723</v>
+        <v>7013878</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -22220,17 +22220,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -22268,10 +22268,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121196381</v>
+        <v>121196729</v>
       </c>
       <c r="B159" t="n">
-        <v>79717</v>
+        <v>98098</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -22280,45 +22280,58 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500872</v>
+        <v>500833</v>
       </c>
       <c r="R159" t="n">
-        <v>7013820</v>
+        <v>7013748</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22355,7 +22368,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22375,32 +22388,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL159" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -22709,7 +22697,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121203688</v>
+        <v>121195472</v>
       </c>
       <c r="B162" t="n">
         <v>98098</v>
@@ -22744,7 +22732,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -22769,13 +22757,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>500200</v>
+        <v>500883</v>
       </c>
       <c r="R162" t="n">
-        <v>7014080</v>
+        <v>7013806</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -22799,17 +22787,17 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -22829,7 +22817,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -22847,7 +22835,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121195472</v>
+        <v>121203724</v>
       </c>
       <c r="B163" t="n">
         <v>98098</v>
@@ -22882,7 +22870,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22907,10 +22895,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500883</v>
+        <v>500179</v>
       </c>
       <c r="R163" t="n">
-        <v>7013806</v>
+        <v>7013960</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -22937,17 +22925,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22967,7 +22955,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22985,10 +22973,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121201748</v>
+        <v>121197288</v>
       </c>
       <c r="B164" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -22997,58 +22985,45 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500205</v>
+        <v>500924</v>
       </c>
       <c r="R164" t="n">
-        <v>7013878</v>
+        <v>7013754</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -23075,17 +23050,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23105,7 +23080,32 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23272,7 +23272,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121318594</v>
+        <v>121318402</v>
       </c>
       <c r="B166" t="n">
         <v>57507</v>
@@ -23324,14 +23324,14 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R166" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -23387,7 +23387,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318402</v>
+        <v>121318594</v>
       </c>
       <c r="B167" t="n">
         <v>57507</v>
@@ -23457,14 +23457,14 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R167" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121339923</v>
+        <v>121335375</v>
       </c>
       <c r="B168" t="n">
-        <v>91396</v>
+        <v>98098</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,53 +23550,58 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500108</v>
+        <v>500170</v>
       </c>
       <c r="R168" t="n">
-        <v>7013909</v>
+        <v>7014032</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23631,6 +23636,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -23648,27 +23658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23686,10 +23676,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339649</v>
+        <v>121338927</v>
       </c>
       <c r="B169" t="n">
-        <v>98098</v>
+        <v>98015</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23698,30 +23688,30 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -23731,7 +23721,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -23746,13 +23736,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500207</v>
+        <v>500220</v>
       </c>
       <c r="R169" t="n">
-        <v>7013937</v>
+        <v>7014127</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -23786,7 +23776,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23806,7 +23796,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23824,10 +23814,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339476</v>
+        <v>121339744</v>
       </c>
       <c r="B170" t="n">
-        <v>98098</v>
+        <v>90731</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23836,58 +23826,53 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500200</v>
+        <v>500169</v>
       </c>
       <c r="R170" t="n">
-        <v>7014028</v>
+        <v>7013982</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -23924,7 +23909,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23944,7 +23929,27 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23962,7 +23967,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339782</v>
+        <v>121339956</v>
       </c>
       <c r="B171" t="n">
         <v>98098</v>
@@ -23997,7 +24002,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -24022,13 +24027,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500152</v>
+        <v>500265</v>
       </c>
       <c r="R171" t="n">
-        <v>7013957</v>
+        <v>7013735</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24062,7 +24067,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24082,7 +24087,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24100,10 +24105,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121339891</v>
+        <v>121337877</v>
       </c>
       <c r="B172" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24112,35 +24117,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N172" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24148,17 +24161,17 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500163</v>
+        <v>500184</v>
       </c>
       <c r="R172" t="n">
-        <v>7013970</v>
+        <v>7014123</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -24192,7 +24205,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24201,6 +24214,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -24211,27 +24225,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24249,10 +24243,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121339861</v>
+        <v>121339649</v>
       </c>
       <c r="B173" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24261,41 +24255,58 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500140</v>
+        <v>500207</v>
       </c>
       <c r="R173" t="n">
-        <v>7013999</v>
+        <v>7013937</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24332,7 +24343,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24352,32 +24363,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL173" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24395,10 +24381,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121335375</v>
+        <v>121339542</v>
       </c>
       <c r="B174" t="n">
-        <v>98098</v>
+        <v>90731</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24407,61 +24393,56 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500170</v>
+        <v>500188</v>
       </c>
       <c r="R174" t="n">
-        <v>7014032</v>
+        <v>7013973</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -24495,7 +24476,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24515,7 +24496,27 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24533,10 +24534,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121338927</v>
+        <v>121339991</v>
       </c>
       <c r="B175" t="n">
-        <v>98015</v>
+        <v>90731</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24545,61 +24546,44 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500220</v>
+        <v>500281</v>
       </c>
       <c r="R175" t="n">
-        <v>7014127</v>
+        <v>7013721</v>
       </c>
       <c r="S175" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -24633,7 +24617,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24653,7 +24637,27 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24671,10 +24675,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339991</v>
+        <v>121339038</v>
       </c>
       <c r="B176" t="n">
-        <v>90731</v>
+        <v>98098</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24683,41 +24687,58 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500281</v>
+        <v>500173</v>
       </c>
       <c r="R176" t="n">
-        <v>7013721</v>
+        <v>7014080</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24754,7 +24775,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24774,27 +24795,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24812,10 +24813,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121337877</v>
+        <v>121339891</v>
       </c>
       <c r="B177" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24824,43 +24825,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24868,17 +24861,17 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500184</v>
+        <v>500163</v>
       </c>
       <c r="R177" t="n">
-        <v>7014123</v>
+        <v>7013970</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24912,7 +24905,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24921,7 +24914,6 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -24932,7 +24924,27 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -25088,10 +25100,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121339542</v>
+        <v>121335603</v>
       </c>
       <c r="B179" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25104,52 +25116,49 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500188</v>
+        <v>500182</v>
       </c>
       <c r="R179" t="n">
-        <v>7013973</v>
+        <v>7014067</v>
       </c>
       <c r="S179" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -25183,7 +25192,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25192,7 +25201,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -25203,7 +25211,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
@@ -25218,12 +25226,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25241,10 +25249,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121335603</v>
+        <v>121339923</v>
       </c>
       <c r="B180" t="n">
-        <v>57354</v>
+        <v>91396</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25253,50 +25261,53 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500182</v>
+        <v>500108</v>
       </c>
       <c r="R180" t="n">
-        <v>7014067</v>
+        <v>7013909</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -25331,17 +25342,13 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -25352,7 +25359,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -25367,12 +25374,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25390,10 +25397,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121340000</v>
+        <v>121339897</v>
       </c>
       <c r="B181" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25402,48 +25409,61 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500299</v>
+        <v>500163</v>
       </c>
       <c r="R181" t="n">
-        <v>7013696</v>
+        <v>7013970</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -25477,7 +25497,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25498,26 +25518,6 @@
       <c r="AI181" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25535,7 +25535,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339897</v>
+        <v>121339476</v>
       </c>
       <c r="B182" t="n">
         <v>98098</v>
@@ -25570,7 +25570,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25591,14 +25591,14 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500163</v>
+        <v>500200</v>
       </c>
       <c r="R182" t="n">
-        <v>7013970</v>
+        <v>7014028</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25673,10 +25673,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339956</v>
+        <v>121339861</v>
       </c>
       <c r="B183" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25685,61 +25685,44 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500265</v>
+        <v>500140</v>
       </c>
       <c r="R183" t="n">
-        <v>7013735</v>
+        <v>7013999</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -25773,7 +25756,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25794,6 +25777,31 @@
       <c r="AI183" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25811,10 +25819,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339744</v>
+        <v>121340000</v>
       </c>
       <c r="B184" t="n">
-        <v>90731</v>
+        <v>90713</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25827,33 +25835,25 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -25866,13 +25866,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500169</v>
+        <v>500299</v>
       </c>
       <c r="R184" t="n">
-        <v>7013982</v>
+        <v>7013696</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
@@ -25941,12 +25941,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25964,7 +25964,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339038</v>
+        <v>121339782</v>
       </c>
       <c r="B185" t="n">
         <v>98098</v>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -26024,10 +26024,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500173</v>
+        <v>500152</v>
       </c>
       <c r="R185" t="n">
-        <v>7014080</v>
+        <v>7013957</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -26064,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -23814,10 +23814,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339744</v>
+        <v>121339956</v>
       </c>
       <c r="B170" t="n">
-        <v>90731</v>
+        <v>98098</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23826,56 +23826,61 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500169</v>
+        <v>500265</v>
       </c>
       <c r="R170" t="n">
-        <v>7013982</v>
+        <v>7013735</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -23909,7 +23914,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23929,27 +23934,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23967,10 +23952,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339956</v>
+        <v>121339744</v>
       </c>
       <c r="B171" t="n">
-        <v>98098</v>
+        <v>90731</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23979,61 +23964,56 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500265</v>
+        <v>500169</v>
       </c>
       <c r="R171" t="n">
-        <v>7013735</v>
+        <v>7013982</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24067,7 +24047,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24087,7 +24067,27 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24675,10 +24675,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339038</v>
+        <v>121339891</v>
       </c>
       <c r="B176" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24687,43 +24687,35 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24731,14 +24723,14 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500173</v>
+        <v>500163</v>
       </c>
       <c r="R176" t="n">
-        <v>7014080</v>
+        <v>7013970</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24775,7 +24767,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24784,7 +24776,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -24795,7 +24786,27 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24813,10 +24824,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121339891</v>
+        <v>121339038</v>
       </c>
       <c r="B177" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24825,35 +24836,43 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24861,14 +24880,14 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500163</v>
+        <v>500173</v>
       </c>
       <c r="R177" t="n">
-        <v>7013970</v>
+        <v>7014080</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -24905,7 +24924,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24914,6 +24933,7 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -24924,27 +24944,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -25819,10 +25819,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121340000</v>
+        <v>121339782</v>
       </c>
       <c r="B184" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25831,48 +25831,61 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500299</v>
+        <v>500152</v>
       </c>
       <c r="R184" t="n">
-        <v>7013696</v>
+        <v>7013957</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -25906,7 +25919,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25926,27 +25939,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25964,10 +25957,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339782</v>
+        <v>121340000</v>
       </c>
       <c r="B185" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25976,61 +25969,48 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500152</v>
+        <v>500299</v>
       </c>
       <c r="R185" t="n">
-        <v>7013957</v>
+        <v>7013696</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26064,7 +26044,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26064,27 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -24675,10 +24675,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339891</v>
+        <v>121339038</v>
       </c>
       <c r="B176" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24687,35 +24687,43 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24723,14 +24731,14 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500163</v>
+        <v>500173</v>
       </c>
       <c r="R176" t="n">
-        <v>7013970</v>
+        <v>7014080</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24767,7 +24775,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24776,6 +24784,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -24786,27 +24795,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24824,10 +24813,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121339038</v>
+        <v>121339891</v>
       </c>
       <c r="B177" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24836,43 +24825,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24880,14 +24861,14 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500173</v>
+        <v>500163</v>
       </c>
       <c r="R177" t="n">
-        <v>7014080</v>
+        <v>7013970</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -24924,7 +24905,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24933,7 +24914,6 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -24944,7 +24924,27 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -25819,10 +25819,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339782</v>
+        <v>121340000</v>
       </c>
       <c r="B184" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25831,61 +25831,48 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500152</v>
+        <v>500299</v>
       </c>
       <c r="R184" t="n">
-        <v>7013957</v>
+        <v>7013696</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -25919,7 +25906,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25939,7 +25926,27 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25957,10 +25964,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121340000</v>
+        <v>121339782</v>
       </c>
       <c r="B185" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25969,48 +25976,61 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500299</v>
+        <v>500152</v>
       </c>
       <c r="R185" t="n">
-        <v>7013696</v>
+        <v>7013957</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26044,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26064,27 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -21018,10 +21018,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121196283</v>
+        <v>121197288</v>
       </c>
       <c r="B150" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -21030,58 +21030,45 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500872</v>
+        <v>500924</v>
       </c>
       <c r="R150" t="n">
-        <v>7013820</v>
+        <v>7013754</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -21118,7 +21105,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21138,7 +21125,32 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21156,10 +21168,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121198065</v>
+        <v>121196283</v>
       </c>
       <c r="B151" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -21191,7 +21203,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21216,10 +21228,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500857</v>
+        <v>500872</v>
       </c>
       <c r="R151" t="n">
-        <v>7013723</v>
+        <v>7013820</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -21256,7 +21268,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21276,7 +21288,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -21294,10 +21306,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121203688</v>
+        <v>121203565</v>
       </c>
       <c r="B152" t="n">
-        <v>98098</v>
+        <v>98021</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21306,30 +21318,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21343,21 +21355,17 @@
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500200</v>
+        <v>500210</v>
       </c>
       <c r="R152" t="n">
-        <v>7014080</v>
+        <v>7014055</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -21394,7 +21402,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21414,7 +21422,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -21432,10 +21440,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121197538</v>
+        <v>121201641</v>
       </c>
       <c r="B153" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -21467,7 +21475,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21477,7 +21485,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -21492,10 +21500,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500895</v>
+        <v>500241</v>
       </c>
       <c r="R153" t="n">
-        <v>7013735</v>
+        <v>7013834</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -21522,17 +21530,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21552,7 +21560,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21570,10 +21578,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121201641</v>
+        <v>121203724</v>
       </c>
       <c r="B154" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -21605,7 +21613,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -21630,10 +21638,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500241</v>
+        <v>500179</v>
       </c>
       <c r="R154" t="n">
-        <v>7013834</v>
+        <v>7013960</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -21670,7 +21678,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -21690,7 +21698,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -21708,10 +21716,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121201394</v>
+        <v>121203688</v>
       </c>
       <c r="B155" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -21743,7 +21751,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -21768,13 +21776,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500242</v>
+        <v>500200</v>
       </c>
       <c r="R155" t="n">
-        <v>7013801</v>
+        <v>7014080</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -21808,7 +21816,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -21828,7 +21836,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -21846,10 +21854,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121203565</v>
+        <v>121201394</v>
       </c>
       <c r="B156" t="n">
-        <v>98015</v>
+        <v>98104</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21858,30 +21866,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -21895,20 +21903,24 @@
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500210</v>
+        <v>500242</v>
       </c>
       <c r="R156" t="n">
-        <v>7014055</v>
+        <v>7013801</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -21942,7 +21954,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -21962,7 +21974,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -21980,10 +21992,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121196381</v>
+        <v>121197538</v>
       </c>
       <c r="B157" t="n">
-        <v>79717</v>
+        <v>98104</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -21992,45 +22004,58 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500872</v>
+        <v>500895</v>
       </c>
       <c r="R157" t="n">
-        <v>7013820</v>
+        <v>7013735</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -22067,7 +22092,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22087,32 +22112,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL157" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22130,10 +22130,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121201748</v>
+        <v>121195472</v>
       </c>
       <c r="B158" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22190,10 +22190,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500205</v>
+        <v>500883</v>
       </c>
       <c r="R158" t="n">
-        <v>7013878</v>
+        <v>7013806</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -22220,17 +22220,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -22268,10 +22268,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121196729</v>
+        <v>121201836</v>
       </c>
       <c r="B159" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -22328,10 +22328,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500833</v>
+        <v>500162</v>
       </c>
       <c r="R159" t="n">
-        <v>7013748</v>
+        <v>7013924</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22358,17 +22358,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -22406,10 +22406,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121201836</v>
+        <v>121196381</v>
       </c>
       <c r="B160" t="n">
-        <v>98098</v>
+        <v>79718</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -22418,58 +22418,45 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500162</v>
+        <v>500872</v>
       </c>
       <c r="R160" t="n">
-        <v>7013924</v>
+        <v>7013820</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -22496,17 +22483,17 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22526,7 +22513,32 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>En lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -22544,10 +22556,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121196322</v>
+        <v>121196729</v>
       </c>
       <c r="B161" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -22556,45 +22568,58 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>500872</v>
+        <v>500833</v>
       </c>
       <c r="R161" t="n">
-        <v>7013820</v>
+        <v>7013748</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -22631,7 +22656,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -22651,35 +22676,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL161" t="inlineStr">
-        <is>
-          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN161" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -22697,10 +22694,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121195472</v>
+        <v>121196322</v>
       </c>
       <c r="B162" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -22709,58 +22706,45 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>500883</v>
+        <v>500872</v>
       </c>
       <c r="R162" t="n">
-        <v>7013806</v>
+        <v>7013820</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -22797,7 +22781,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Knärot med minst 340 st skott/stjälkar och 2 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -22818,6 +22802,34 @@
       <c r="AI162" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -22835,10 +22847,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121203724</v>
+        <v>121201748</v>
       </c>
       <c r="B163" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -22870,7 +22882,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22895,10 +22907,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500179</v>
+        <v>500205</v>
       </c>
       <c r="R163" t="n">
-        <v>7013960</v>
+        <v>7013878</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -22935,7 +22947,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22955,7 +22967,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22973,10 +22985,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121197288</v>
+        <v>121198065</v>
       </c>
       <c r="B164" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -22985,45 +22997,58 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500924</v>
+        <v>500857</v>
       </c>
       <c r="R164" t="n">
-        <v>7013754</v>
+        <v>7013723</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -23060,7 +23085,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23080,32 +23105,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>En skadad död stående sälgstam.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318473</v>
+        <v>121318594</v>
       </c>
       <c r="B165" t="n">
-        <v>90709</v>
+        <v>57508</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,45 +23139,50 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R165" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -23223,7 +23228,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23234,27 +23238,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23275,7 +23259,7 @@
         <v>121318402</v>
       </c>
       <c r="B166" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -23405,10 +23389,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318594</v>
+        <v>121318473</v>
       </c>
       <c r="B167" t="n">
-        <v>57507</v>
+        <v>90715</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23421,50 +23405,45 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R167" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -23510,6 +23489,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -23520,7 +23500,27 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121335375</v>
+        <v>121339991</v>
       </c>
       <c r="B168" t="n">
-        <v>98098</v>
+        <v>90737</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,58 +23550,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500170</v>
+        <v>500281</v>
       </c>
       <c r="R168" t="n">
-        <v>7014032</v>
+        <v>7013721</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23638,7 +23621,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23658,7 +23641,27 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23676,10 +23679,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121338927</v>
+        <v>121339744</v>
       </c>
       <c r="B169" t="n">
-        <v>98015</v>
+        <v>90737</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23688,61 +23691,56 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500220</v>
+        <v>500169</v>
       </c>
       <c r="R169" t="n">
-        <v>7014127</v>
+        <v>7013982</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -23796,7 +23794,27 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23814,10 +23832,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339956</v>
+        <v>121339476</v>
       </c>
       <c r="B170" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23849,7 +23867,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -23874,13 +23892,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500265</v>
+        <v>500200</v>
       </c>
       <c r="R170" t="n">
-        <v>7013735</v>
+        <v>7014028</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -23914,7 +23932,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23934,7 +23952,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23952,10 +23970,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339744</v>
+        <v>121339649</v>
       </c>
       <c r="B171" t="n">
-        <v>90731</v>
+        <v>98104</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23964,53 +23982,58 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500169</v>
+        <v>500207</v>
       </c>
       <c r="R171" t="n">
-        <v>7013982</v>
+        <v>7013937</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -24047,7 +24070,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24067,27 +24090,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24105,10 +24108,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121337877</v>
+        <v>121339956</v>
       </c>
       <c r="B172" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24140,7 +24143,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -24165,10 +24168,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500184</v>
+        <v>500265</v>
       </c>
       <c r="R172" t="n">
-        <v>7014123</v>
+        <v>7013735</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -24205,7 +24208,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24225,7 +24228,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24243,10 +24246,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121339649</v>
+        <v>121338927</v>
       </c>
       <c r="B173" t="n">
-        <v>98098</v>
+        <v>98021</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24255,30 +24258,30 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -24288,7 +24291,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
@@ -24303,13 +24306,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500207</v>
+        <v>500220</v>
       </c>
       <c r="R173" t="n">
-        <v>7013937</v>
+        <v>7014127</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -24343,7 +24346,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24363,7 +24366,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24381,10 +24384,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121339542</v>
+        <v>121335375</v>
       </c>
       <c r="B174" t="n">
-        <v>90731</v>
+        <v>98104</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24393,56 +24396,61 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500188</v>
+        <v>500170</v>
       </c>
       <c r="R174" t="n">
-        <v>7013973</v>
+        <v>7014032</v>
       </c>
       <c r="S174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -24476,7 +24484,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24496,27 +24504,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24534,10 +24522,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121339991</v>
+        <v>121339923</v>
       </c>
       <c r="B175" t="n">
-        <v>90731</v>
+        <v>91402</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24546,30 +24534,42 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -24577,10 +24577,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500281</v>
+        <v>500108</v>
       </c>
       <c r="R175" t="n">
-        <v>7013721</v>
+        <v>7013909</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -24615,11 +24615,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -24652,12 +24647,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24675,10 +24670,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339038</v>
+        <v>121335603</v>
       </c>
       <c r="B176" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24687,43 +24682,35 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24731,14 +24718,14 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500173</v>
+        <v>500182</v>
       </c>
       <c r="R176" t="n">
-        <v>7014080</v>
+        <v>7014067</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24775,7 +24762,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24784,7 +24771,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -24795,7 +24781,27 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24813,10 +24819,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121339891</v>
+        <v>121337877</v>
       </c>
       <c r="B177" t="n">
-        <v>57354</v>
+        <v>98104</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24825,35 +24831,43 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24861,17 +24875,17 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500163</v>
+        <v>500184</v>
       </c>
       <c r="R177" t="n">
-        <v>7013970</v>
+        <v>7014123</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24905,7 +24919,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24914,6 +24928,7 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -24924,27 +24939,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24965,7 +24960,7 @@
         <v>121338977</v>
       </c>
       <c r="B178" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -25100,10 +25095,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121335603</v>
+        <v>121339782</v>
       </c>
       <c r="B179" t="n">
-        <v>57354</v>
+        <v>98104</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25112,35 +25107,43 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N179" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25148,14 +25151,14 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500182</v>
+        <v>500152</v>
       </c>
       <c r="R179" t="n">
-        <v>7014067</v>
+        <v>7013957</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -25192,7 +25195,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25201,6 +25204,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -25211,27 +25215,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25249,10 +25233,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121339923</v>
+        <v>121339542</v>
       </c>
       <c r="B180" t="n">
-        <v>91396</v>
+        <v>90737</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25261,30 +25245,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -25304,13 +25288,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500108</v>
+        <v>500188</v>
       </c>
       <c r="R180" t="n">
-        <v>7013909</v>
+        <v>7013973</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -25340,6 +25324,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25359,7 +25348,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -25374,12 +25363,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25397,10 +25386,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121339897</v>
+        <v>121339861</v>
       </c>
       <c r="B181" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25409,58 +25398,41 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500163</v>
+        <v>500140</v>
       </c>
       <c r="R181" t="n">
-        <v>7013970</v>
+        <v>7013999</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -25497,7 +25469,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25518,6 +25490,31 @@
       <c r="AI181" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25535,10 +25532,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339476</v>
+        <v>121339891</v>
       </c>
       <c r="B182" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25547,43 +25544,35 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25591,14 +25580,14 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500200</v>
+        <v>500163</v>
       </c>
       <c r="R182" t="n">
-        <v>7014028</v>
+        <v>7013970</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -25635,7 +25624,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25644,7 +25633,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -25655,7 +25643,27 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25673,10 +25681,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339861</v>
+        <v>121339038</v>
       </c>
       <c r="B183" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25685,41 +25693,58 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500140</v>
+        <v>500173</v>
       </c>
       <c r="R183" t="n">
-        <v>7013999</v>
+        <v>7014080</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -25756,7 +25781,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25776,32 +25801,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL183" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25819,10 +25819,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121340000</v>
+        <v>121339897</v>
       </c>
       <c r="B184" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25831,48 +25831,61 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500299</v>
+        <v>500163</v>
       </c>
       <c r="R184" t="n">
-        <v>7013696</v>
+        <v>7013970</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -25906,7 +25919,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -25927,26 +25940,6 @@
       <c r="AI184" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25964,10 +25957,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339782</v>
+        <v>121340000</v>
       </c>
       <c r="B185" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25976,61 +25969,48 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500152</v>
+        <v>500299</v>
       </c>
       <c r="R185" t="n">
-        <v>7013957</v>
+        <v>7013696</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26064,7 +26044,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26064,27 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -23679,10 +23679,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339744</v>
+        <v>121339476</v>
       </c>
       <c r="B169" t="n">
-        <v>90737</v>
+        <v>98104</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23691,53 +23691,58 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500169</v>
+        <v>500200</v>
       </c>
       <c r="R169" t="n">
-        <v>7013982</v>
+        <v>7014028</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -23774,7 +23779,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23794,27 +23799,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23832,10 +23817,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339476</v>
+        <v>121339744</v>
       </c>
       <c r="B170" t="n">
-        <v>98104</v>
+        <v>90737</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23844,58 +23829,53 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500200</v>
+        <v>500169</v>
       </c>
       <c r="R170" t="n">
-        <v>7014028</v>
+        <v>7013982</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -23932,7 +23912,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23952,7 +23932,27 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -21018,10 +21018,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121197288</v>
+        <v>121203688</v>
       </c>
       <c r="B150" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -21030,48 +21030,61 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>500924</v>
+        <v>500200</v>
       </c>
       <c r="R150" t="n">
-        <v>7013754</v>
+        <v>7014080</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -21095,17 +21108,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -21125,32 +21138,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL150" t="inlineStr">
-        <is>
-          <t>En skadad död stående sälgstam.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -21168,10 +21156,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121196283</v>
+        <v>121203565</v>
       </c>
       <c r="B151" t="n">
-        <v>98104</v>
+        <v>98022</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -21180,30 +21168,30 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21217,24 +21205,20 @@
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>500872</v>
+        <v>500210</v>
       </c>
       <c r="R151" t="n">
-        <v>7013820</v>
+        <v>7014055</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -21258,17 +21242,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -21288,7 +21272,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -21306,10 +21290,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121203565</v>
+        <v>121197538</v>
       </c>
       <c r="B152" t="n">
-        <v>98021</v>
+        <v>98105</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21318,30 +21302,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21351,24 +21335,28 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>500210</v>
+        <v>500895</v>
       </c>
       <c r="R152" t="n">
-        <v>7014055</v>
+        <v>7013735</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -21392,17 +21380,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Minst 2 st. fröställningar av fläcknycklar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -21422,7 +21410,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -21440,10 +21428,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121201641</v>
+        <v>121196729</v>
       </c>
       <c r="B153" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -21475,7 +21463,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21500,10 +21488,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>500241</v>
+        <v>500833</v>
       </c>
       <c r="R153" t="n">
-        <v>7013834</v>
+        <v>7013748</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -21530,17 +21518,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -21560,7 +21548,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21578,10 +21566,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121203724</v>
+        <v>121201394</v>
       </c>
       <c r="B154" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -21613,7 +21601,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -21638,10 +21626,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>500179</v>
+        <v>500242</v>
       </c>
       <c r="R154" t="n">
-        <v>7013960</v>
+        <v>7013801</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -21678,7 +21666,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -21698,7 +21686,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -21716,10 +21704,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121203688</v>
+        <v>121196381</v>
       </c>
       <c r="B155" t="n">
-        <v>98104</v>
+        <v>79719</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -21728,61 +21716,48 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>500200</v>
+        <v>500872</v>
       </c>
       <c r="R155" t="n">
-        <v>7014080</v>
+        <v>7013820</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -21806,17 +21781,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Fina exemplar av stuplav på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -21836,7 +21811,32 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Grandominerad gammal och luckig skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med död ved.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>En lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -21854,10 +21854,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121201394</v>
+        <v>121196322</v>
       </c>
       <c r="B156" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21866,58 +21866,45 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>500242</v>
+        <v>500872</v>
       </c>
       <c r="R156" t="n">
-        <v>7013801</v>
+        <v>7013820</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -21944,17 +21931,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Knärot med minst 200 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -21974,7 +21961,35 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -21992,10 +22007,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121197538</v>
+        <v>121201641</v>
       </c>
       <c r="B157" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -22027,7 +22042,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -22037,7 +22052,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -22052,10 +22067,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>500895</v>
+        <v>500241</v>
       </c>
       <c r="R157" t="n">
-        <v>7013735</v>
+        <v>7013834</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -22082,17 +22097,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Knärot med minst 30 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar och 5 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -22112,7 +22127,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -22133,7 +22148,7 @@
         <v>121195472</v>
       </c>
       <c r="B158" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -22268,10 +22283,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121201836</v>
+        <v>121197288</v>
       </c>
       <c r="B159" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -22280,58 +22295,45 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>500162</v>
+        <v>500924</v>
       </c>
       <c r="R159" t="n">
-        <v>7013924</v>
+        <v>7013754</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -22358,17 +22360,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Lunglav på en död stående sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22388,7 +22390,32 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>En skadad död stående sälgstam.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En skadad död stående sälgstam.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -22406,10 +22433,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121196381</v>
+        <v>121203724</v>
       </c>
       <c r="B160" t="n">
-        <v>79718</v>
+        <v>98105</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -22418,45 +22445,58 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>500872</v>
+        <v>500179</v>
       </c>
       <c r="R160" t="n">
-        <v>7013820</v>
+        <v>7013960</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -22483,17 +22523,17 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Fina exemplar av stuplav på en lutande sälg.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -22513,32 +22553,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>En lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En lutande smal sälg.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Träd med socklar. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -22556,10 +22571,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121196729</v>
+        <v>121196283</v>
       </c>
       <c r="B161" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -22591,7 +22606,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -22616,10 +22631,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>500833</v>
+        <v>500872</v>
       </c>
       <c r="R161" t="n">
-        <v>7013748</v>
+        <v>7013820</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -22656,7 +22671,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Knärot med minst 35 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 19 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -22676,7 +22691,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Gott om klenvuxna träd. Bitvis måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -22694,10 +22709,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121196322</v>
+        <v>121198065</v>
       </c>
       <c r="B162" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -22706,45 +22721,58 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>500872</v>
+        <v>500857</v>
       </c>
       <c r="R162" t="n">
-        <v>7013820</v>
+        <v>7013723</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -22781,7 +22809,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på sälg. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -22801,35 +22829,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Spår av hackspettar. Även spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>En rakväxt smal sälg och en lutande smal sälg.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN162" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Bark on living woody plant # Salix caprea # En rakväxt smal sälg och en lutande smal sälg.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -22847,10 +22847,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121201748</v>
+        <v>121201836</v>
       </c>
       <c r="B163" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -22907,10 +22907,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>500205</v>
+        <v>500162</v>
       </c>
       <c r="R163" t="n">
-        <v>7013878</v>
+        <v>7013924</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 2 st fröställningar inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och frisk mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -22985,10 +22985,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121198065</v>
+        <v>121201748</v>
       </c>
       <c r="B164" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -23045,10 +23045,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500857</v>
+        <v>500205</v>
       </c>
       <c r="R164" t="n">
-        <v>7013723</v>
+        <v>7013878</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -23075,17 +23075,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis gott om klenvuxna träd och måttliga mängder med liggande och stående död ved. Spår av äldre skogsbrand i form av kolade stubbar. Bottenskikt med mossor och fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad skog med olikåldriga träd på frisk-fuktig och fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
         <v>121318594</v>
       </c>
       <c r="B165" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23256,10 +23256,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121318402</v>
+        <v>121318473</v>
       </c>
       <c r="B166" t="n">
-        <v>57508</v>
+        <v>90716</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -23272,40 +23272,35 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23361,6 +23356,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -23372,6 +23368,26 @@
       <c r="AI166" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -23389,10 +23405,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318473</v>
+        <v>121318402</v>
       </c>
       <c r="B167" t="n">
-        <v>90715</v>
+        <v>57509</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23405,35 +23421,40 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23489,7 +23510,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -23501,26 +23521,6 @@
       <c r="AI167" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121339991</v>
+        <v>121339782</v>
       </c>
       <c r="B168" t="n">
-        <v>90737</v>
+        <v>98105</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,41 +23550,58 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500281</v>
+        <v>500152</v>
       </c>
       <c r="R168" t="n">
-        <v>7013721</v>
+        <v>7013957</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23621,7 +23638,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23641,27 +23658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23679,10 +23676,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339476</v>
+        <v>121339891</v>
       </c>
       <c r="B169" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23691,43 +23688,35 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -23735,14 +23724,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500200</v>
+        <v>500163</v>
       </c>
       <c r="R169" t="n">
-        <v>7014028</v>
+        <v>7013970</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -23779,7 +23768,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23788,7 +23777,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -23799,7 +23787,27 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23817,10 +23825,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339744</v>
+        <v>121339861</v>
       </c>
       <c r="B170" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23833,38 +23841,26 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -23872,10 +23868,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500169</v>
+        <v>500140</v>
       </c>
       <c r="R170" t="n">
-        <v>7013982</v>
+        <v>7013999</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -23912,7 +23908,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -23932,7 +23928,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
@@ -23945,14 +23941,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23970,10 +23971,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339649</v>
+        <v>121339542</v>
       </c>
       <c r="B171" t="n">
-        <v>98104</v>
+        <v>90738</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23982,61 +23983,56 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500207</v>
+        <v>500188</v>
       </c>
       <c r="R171" t="n">
-        <v>7013937</v>
+        <v>7013973</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24070,7 +24066,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24091,6 +24087,26 @@
       <c r="AI171" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24108,10 +24124,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121339956</v>
+        <v>121340000</v>
       </c>
       <c r="B172" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24120,58 +24136,45 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500265</v>
+        <v>500299</v>
       </c>
       <c r="R172" t="n">
-        <v>7013735</v>
+        <v>7013696</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -24208,7 +24211,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24229,6 +24232,26 @@
       <c r="AI172" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24246,10 +24269,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121338927</v>
+        <v>121335603</v>
       </c>
       <c r="B173" t="n">
-        <v>98021</v>
+        <v>57356</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24258,43 +24281,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N173" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24302,17 +24317,17 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500220</v>
+        <v>500182</v>
       </c>
       <c r="R173" t="n">
-        <v>7014127</v>
+        <v>7014067</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -24346,7 +24361,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24355,7 +24370,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -24366,7 +24380,27 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24384,10 +24418,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121335375</v>
+        <v>121339897</v>
       </c>
       <c r="B174" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24419,7 +24453,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -24440,14 +24474,14 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500170</v>
+        <v>500163</v>
       </c>
       <c r="R174" t="n">
-        <v>7014032</v>
+        <v>7013970</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -24484,7 +24518,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24504,7 +24538,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24522,10 +24556,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121339923</v>
+        <v>121339956</v>
       </c>
       <c r="B175" t="n">
-        <v>91402</v>
+        <v>98105</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24534,56 +24568,61 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500108</v>
+        <v>500265</v>
       </c>
       <c r="R175" t="n">
-        <v>7013909</v>
+        <v>7013735</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -24613,6 +24652,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24633,26 +24677,6 @@
       <c r="AI175" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24670,10 +24694,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121335603</v>
+        <v>121339476</v>
       </c>
       <c r="B176" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24682,35 +24706,43 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24718,14 +24750,14 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500182</v>
+        <v>500200</v>
       </c>
       <c r="R176" t="n">
-        <v>7014067</v>
+        <v>7014028</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24762,7 +24794,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24771,6 +24803,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -24781,27 +24814,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24819,10 +24832,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121337877</v>
+        <v>121335375</v>
       </c>
       <c r="B177" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24879,13 +24892,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500184</v>
+        <v>500170</v>
       </c>
       <c r="R177" t="n">
-        <v>7014123</v>
+        <v>7014032</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24919,7 +24932,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24939,7 +24952,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24957,10 +24970,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121338977</v>
+        <v>121339649</v>
       </c>
       <c r="B178" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -24992,7 +25005,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -25017,13 +25030,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500191</v>
+        <v>500207</v>
       </c>
       <c r="R178" t="n">
-        <v>7014126</v>
+        <v>7013937</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -25057,7 +25070,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25077,7 +25090,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25095,10 +25108,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121339782</v>
+        <v>121339991</v>
       </c>
       <c r="B179" t="n">
-        <v>98104</v>
+        <v>90738</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25107,58 +25120,41 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500152</v>
+        <v>500281</v>
       </c>
       <c r="R179" t="n">
-        <v>7013957</v>
+        <v>7013721</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -25195,7 +25191,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25215,7 +25211,27 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25233,10 +25249,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121339542</v>
+        <v>121338977</v>
       </c>
       <c r="B180" t="n">
-        <v>90737</v>
+        <v>98105</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25245,53 +25261,58 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500188</v>
+        <v>500191</v>
       </c>
       <c r="R180" t="n">
-        <v>7013973</v>
+        <v>7014126</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -25328,7 +25349,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25348,27 +25369,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25386,10 +25387,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121339861</v>
+        <v>121337877</v>
       </c>
       <c r="B181" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25398,44 +25399,61 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500140</v>
+        <v>500184</v>
       </c>
       <c r="R181" t="n">
-        <v>7013999</v>
+        <v>7014123</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -25469,7 +25487,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25489,32 +25507,7 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL181" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25532,10 +25525,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339891</v>
+        <v>121338927</v>
       </c>
       <c r="B182" t="n">
-        <v>57355</v>
+        <v>98022</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25544,35 +25537,43 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N182" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25580,17 +25581,17 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500163</v>
+        <v>500220</v>
       </c>
       <c r="R182" t="n">
-        <v>7013970</v>
+        <v>7014127</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -25624,7 +25625,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25633,6 +25634,7 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -25643,27 +25645,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25681,10 +25663,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339038</v>
+        <v>121339744</v>
       </c>
       <c r="B183" t="n">
-        <v>98104</v>
+        <v>90738</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25693,58 +25675,53 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500173</v>
+        <v>500169</v>
       </c>
       <c r="R183" t="n">
-        <v>7014080</v>
+        <v>7013982</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -25781,7 +25758,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -25801,7 +25778,27 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25819,10 +25816,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339897</v>
+        <v>121339923</v>
       </c>
       <c r="B184" t="n">
-        <v>98104</v>
+        <v>91403</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25831,58 +25828,53 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500163</v>
+        <v>500108</v>
       </c>
       <c r="R184" t="n">
-        <v>7013970</v>
+        <v>7013909</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -25917,11 +25909,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25940,6 +25927,26 @@
       <c r="AI184" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25957,10 +25964,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121340000</v>
+        <v>121339038</v>
       </c>
       <c r="B185" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25969,48 +25976,61 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500299</v>
+        <v>500173</v>
       </c>
       <c r="R185" t="n">
-        <v>7013696</v>
+        <v>7014080</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26044,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26064,27 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -23123,7 +23123,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318594</v>
+        <v>121318402</v>
       </c>
       <c r="B165" t="n">
         <v>57509</v>
@@ -23175,14 +23175,14 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R165" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23256,10 +23256,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121318473</v>
+        <v>121318594</v>
       </c>
       <c r="B166" t="n">
-        <v>90716</v>
+        <v>57509</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -23272,45 +23272,50 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R166" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -23356,7 +23361,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -23367,27 +23371,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -23405,10 +23389,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318402</v>
+        <v>121318473</v>
       </c>
       <c r="B167" t="n">
-        <v>57509</v>
+        <v>90716</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23421,40 +23405,35 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23510,6 +23489,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -23521,6 +23501,26 @@
       <c r="AI167" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121339782</v>
+        <v>121335603</v>
       </c>
       <c r="B168" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,43 +23550,35 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -23594,14 +23586,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500152</v>
+        <v>500182</v>
       </c>
       <c r="R168" t="n">
-        <v>7013957</v>
+        <v>7014067</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -23638,7 +23630,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23647,7 +23639,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -23658,7 +23649,27 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23825,10 +23836,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339861</v>
+        <v>121339923</v>
       </c>
       <c r="B170" t="n">
-        <v>78609</v>
+        <v>91403</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23837,30 +23848,42 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -23868,10 +23891,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500140</v>
+        <v>500108</v>
       </c>
       <c r="R170" t="n">
-        <v>7013999</v>
+        <v>7013909</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -23906,11 +23929,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -23941,19 +23959,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL170" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23971,10 +23984,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339542</v>
+        <v>121338927</v>
       </c>
       <c r="B171" t="n">
-        <v>90738</v>
+        <v>98022</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23983,53 +23996,58 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500188</v>
+        <v>500220</v>
       </c>
       <c r="R171" t="n">
-        <v>7013973</v>
+        <v>7014127</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -24066,7 +24084,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24086,27 +24104,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24124,10 +24122,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121340000</v>
+        <v>121338977</v>
       </c>
       <c r="B172" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24136,45 +24134,58 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500299</v>
+        <v>500191</v>
       </c>
       <c r="R172" t="n">
-        <v>7013696</v>
+        <v>7014126</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -24211,7 +24222,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24231,27 +24242,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24269,10 +24260,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121335603</v>
+        <v>121335375</v>
       </c>
       <c r="B173" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24281,35 +24272,43 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N173" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24317,14 +24316,14 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500182</v>
+        <v>500170</v>
       </c>
       <c r="R173" t="n">
-        <v>7014067</v>
+        <v>7014032</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24361,7 +24360,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24370,6 +24369,7 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -24380,27 +24380,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24418,10 +24398,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121339897</v>
+        <v>121339542</v>
       </c>
       <c r="B174" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24430,61 +24410,56 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500163</v>
+        <v>500188</v>
       </c>
       <c r="R174" t="n">
-        <v>7013970</v>
+        <v>7013973</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -24518,7 +24493,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24538,7 +24513,27 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24556,10 +24551,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121339956</v>
+        <v>121339861</v>
       </c>
       <c r="B175" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24568,61 +24563,44 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500265</v>
+        <v>500140</v>
       </c>
       <c r="R175" t="n">
-        <v>7013735</v>
+        <v>7013999</v>
       </c>
       <c r="S175" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -24656,7 +24634,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24677,6 +24655,31 @@
       <c r="AI175" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24694,7 +24697,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339476</v>
+        <v>121339897</v>
       </c>
       <c r="B176" t="n">
         <v>98105</v>
@@ -24729,7 +24732,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -24750,14 +24753,14 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500200</v>
+        <v>500163</v>
       </c>
       <c r="R176" t="n">
-        <v>7014028</v>
+        <v>7013970</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24794,7 +24797,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24814,7 +24817,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24832,7 +24835,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121335375</v>
+        <v>121339782</v>
       </c>
       <c r="B177" t="n">
         <v>98105</v>
@@ -24867,7 +24870,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -24892,10 +24895,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500170</v>
+        <v>500152</v>
       </c>
       <c r="R177" t="n">
-        <v>7014032</v>
+        <v>7013957</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -24932,7 +24935,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24952,7 +24955,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24970,7 +24973,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121339649</v>
+        <v>121339038</v>
       </c>
       <c r="B178" t="n">
         <v>98105</v>
@@ -25005,7 +25008,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -25015,7 +25018,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -25030,10 +25033,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500207</v>
+        <v>500173</v>
       </c>
       <c r="R178" t="n">
-        <v>7013937</v>
+        <v>7014080</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -25070,7 +25073,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25090,7 +25093,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25108,10 +25111,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121339991</v>
+        <v>121339649</v>
       </c>
       <c r="B179" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25120,41 +25123,58 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500281</v>
+        <v>500207</v>
       </c>
       <c r="R179" t="n">
-        <v>7013721</v>
+        <v>7013937</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -25191,7 +25211,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25211,27 +25231,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25249,7 +25249,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121338977</v>
+        <v>121339476</v>
       </c>
       <c r="B180" t="n">
         <v>98105</v>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -25294,7 +25294,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -25309,13 +25309,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500191</v>
+        <v>500200</v>
       </c>
       <c r="R180" t="n">
-        <v>7014126</v>
+        <v>7014028</v>
       </c>
       <c r="S180" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25525,10 +25525,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121338927</v>
+        <v>121339956</v>
       </c>
       <c r="B182" t="n">
-        <v>98022</v>
+        <v>98105</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25537,30 +25537,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25585,10 +25585,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500220</v>
+        <v>500265</v>
       </c>
       <c r="R182" t="n">
-        <v>7014127</v>
+        <v>7013735</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25625,7 +25625,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25645,7 +25645,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25816,10 +25816,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339923</v>
+        <v>121339991</v>
       </c>
       <c r="B184" t="n">
-        <v>91403</v>
+        <v>90738</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25828,42 +25828,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -25871,10 +25859,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500108</v>
+        <v>500281</v>
       </c>
       <c r="R184" t="n">
-        <v>7013909</v>
+        <v>7013721</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -25909,6 +25897,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25941,12 +25934,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25964,10 +25957,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339038</v>
+        <v>121340000</v>
       </c>
       <c r="B185" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25976,61 +25969,48 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500173</v>
+        <v>500299</v>
       </c>
       <c r="R185" t="n">
-        <v>7014080</v>
+        <v>7013696</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26064,7 +26044,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26084,7 +26064,27 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318402</v>
+        <v>121318473</v>
       </c>
       <c r="B165" t="n">
-        <v>57509</v>
+        <v>90716</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,40 +23139,35 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23228,6 +23223,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23239,6 +23235,26 @@
       <c r="AI165" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23389,10 +23405,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121318473</v>
+        <v>121318402</v>
       </c>
       <c r="B167" t="n">
-        <v>90716</v>
+        <v>57509</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -23405,35 +23421,40 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
@@ -23489,7 +23510,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -23501,26 +23521,6 @@
       <c r="AI167" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121335603</v>
+        <v>121340000</v>
       </c>
       <c r="B168" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23554,49 +23554,44 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500182</v>
+        <v>500299</v>
       </c>
       <c r="R168" t="n">
-        <v>7014067</v>
+        <v>7013696</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -23630,7 +23625,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23639,6 +23634,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -23649,7 +23645,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
@@ -23664,12 +23660,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23687,10 +23683,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121339891</v>
+        <v>121337877</v>
       </c>
       <c r="B169" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -23699,35 +23695,43 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -23735,17 +23739,17 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500163</v>
+        <v>500184</v>
       </c>
       <c r="R169" t="n">
-        <v>7013970</v>
+        <v>7014123</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -23779,7 +23783,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23788,6 +23792,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -23798,27 +23803,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23836,10 +23821,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121339923</v>
+        <v>121339649</v>
       </c>
       <c r="B170" t="n">
-        <v>91403</v>
+        <v>98105</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -23848,53 +23833,58 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>500108</v>
+        <v>500207</v>
       </c>
       <c r="R170" t="n">
-        <v>7013909</v>
+        <v>7013937</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -23929,6 +23919,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -23946,27 +23941,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -23984,10 +23959,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121338927</v>
+        <v>121339956</v>
       </c>
       <c r="B171" t="n">
-        <v>98022</v>
+        <v>98105</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23996,30 +23971,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -24044,10 +24019,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500220</v>
+        <v>500265</v>
       </c>
       <c r="R171" t="n">
-        <v>7014127</v>
+        <v>7013735</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -24084,7 +24059,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24104,7 +24079,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24122,10 +24097,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121338977</v>
+        <v>121339891</v>
       </c>
       <c r="B172" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24134,43 +24109,35 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N172" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24178,17 +24145,17 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>500191</v>
+        <v>500163</v>
       </c>
       <c r="R172" t="n">
-        <v>7014126</v>
+        <v>7013970</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -24222,7 +24189,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24231,7 +24198,6 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -24242,7 +24208,27 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24260,7 +24246,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121335375</v>
+        <v>121339476</v>
       </c>
       <c r="B173" t="n">
         <v>98105</v>
@@ -24295,7 +24281,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -24320,10 +24306,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500170</v>
+        <v>500200</v>
       </c>
       <c r="R173" t="n">
-        <v>7014032</v>
+        <v>7014028</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -24360,7 +24346,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24380,7 +24366,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24398,10 +24384,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121339542</v>
+        <v>121339782</v>
       </c>
       <c r="B174" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24410,56 +24396,61 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500188</v>
+        <v>500152</v>
       </c>
       <c r="R174" t="n">
-        <v>7013973</v>
+        <v>7013957</v>
       </c>
       <c r="S174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -24493,7 +24484,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24513,27 +24504,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24551,10 +24522,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121339861</v>
+        <v>121335603</v>
       </c>
       <c r="B175" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24567,37 +24538,46 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500140</v>
+        <v>500182</v>
       </c>
       <c r="R175" t="n">
-        <v>7013999</v>
+        <v>7014067</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -24634,7 +24614,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24643,7 +24623,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -24654,7 +24633,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -24667,19 +24646,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL175" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24697,10 +24671,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339897</v>
+        <v>121339744</v>
       </c>
       <c r="B176" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24709,58 +24683,53 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500163</v>
+        <v>500169</v>
       </c>
       <c r="R176" t="n">
-        <v>7013970</v>
+        <v>7013982</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -24797,7 +24766,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24817,7 +24786,27 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24835,7 +24824,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121339782</v>
+        <v>121338977</v>
       </c>
       <c r="B177" t="n">
         <v>98105</v>
@@ -24870,7 +24859,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -24880,7 +24869,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -24895,13 +24884,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500152</v>
+        <v>500191</v>
       </c>
       <c r="R177" t="n">
-        <v>7013957</v>
+        <v>7014126</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24935,7 +24924,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24955,7 +24944,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -25111,7 +25100,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121339649</v>
+        <v>121335375</v>
       </c>
       <c r="B179" t="n">
         <v>98105</v>
@@ -25146,7 +25135,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -25156,7 +25145,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
@@ -25171,10 +25160,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500207</v>
+        <v>500170</v>
       </c>
       <c r="R179" t="n">
-        <v>7013937</v>
+        <v>7014032</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -25211,7 +25200,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Knärot med minst 40 st skott/stjälkar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25231,7 +25220,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25249,10 +25238,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121339476</v>
+        <v>121339991</v>
       </c>
       <c r="B180" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25261,58 +25250,41 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500200</v>
+        <v>500281</v>
       </c>
       <c r="R180" t="n">
-        <v>7014028</v>
+        <v>7013721</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -25349,7 +25321,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25369,7 +25341,27 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25387,10 +25379,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121337877</v>
+        <v>121339542</v>
       </c>
       <c r="B181" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25399,58 +25391,53 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500184</v>
+        <v>500188</v>
       </c>
       <c r="R181" t="n">
-        <v>7014123</v>
+        <v>7013973</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25487,7 +25474,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25507,7 +25494,27 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25525,7 +25532,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339956</v>
+        <v>121339897</v>
       </c>
       <c r="B182" t="n">
         <v>98105</v>
@@ -25560,7 +25567,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25581,17 +25588,17 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500265</v>
+        <v>500163</v>
       </c>
       <c r="R182" t="n">
-        <v>7013735</v>
+        <v>7013970</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -25625,7 +25632,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25663,10 +25670,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121339744</v>
+        <v>121338927</v>
       </c>
       <c r="B183" t="n">
-        <v>90738</v>
+        <v>98022</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25675,56 +25682,61 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500169</v>
+        <v>500220</v>
       </c>
       <c r="R183" t="n">
-        <v>7013982</v>
+        <v>7014127</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -25778,27 +25790,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25816,10 +25808,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339991</v>
+        <v>121339923</v>
       </c>
       <c r="B184" t="n">
-        <v>90738</v>
+        <v>91403</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25828,30 +25820,42 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -25859,10 +25863,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500281</v>
+        <v>500108</v>
       </c>
       <c r="R184" t="n">
-        <v>7013721</v>
+        <v>7013909</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -25897,11 +25901,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25934,12 +25933,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25957,10 +25956,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121340000</v>
+        <v>121339861</v>
       </c>
       <c r="B185" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25973,30 +25972,26 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -26004,13 +25999,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500299</v>
+        <v>500140</v>
       </c>
       <c r="R185" t="n">
-        <v>7013696</v>
+        <v>7013999</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -26044,7 +26039,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26077,14 +26072,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -23123,10 +23123,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121318473</v>
+        <v>121318594</v>
       </c>
       <c r="B165" t="n">
-        <v>90716</v>
+        <v>57509</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -23139,45 +23139,50 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>500178</v>
+        <v>500210</v>
       </c>
       <c r="R165" t="n">
-        <v>7013855</v>
+        <v>7014149</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -23223,7 +23228,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -23234,27 +23238,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -23272,10 +23256,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121318594</v>
+        <v>121318473</v>
       </c>
       <c r="B166" t="n">
-        <v>57509</v>
+        <v>90716</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -23288,50 +23272,45 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>500210</v>
+        <v>500178</v>
       </c>
       <c r="R166" t="n">
-        <v>7014149</v>
+        <v>7013855</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -23377,6 +23356,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -23387,7 +23367,27 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärsris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -23538,10 +23538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121340000</v>
+        <v>121337877</v>
       </c>
       <c r="B168" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -23550,45 +23550,58 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>500299</v>
+        <v>500184</v>
       </c>
       <c r="R168" t="n">
-        <v>7013696</v>
+        <v>7014123</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -23625,7 +23638,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -23645,27 +23658,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -23683,7 +23676,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121337877</v>
+        <v>121339038</v>
       </c>
       <c r="B169" t="n">
         <v>98105</v>
@@ -23718,7 +23711,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -23743,13 +23736,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>500184</v>
+        <v>500173</v>
       </c>
       <c r="R169" t="n">
-        <v>7014123</v>
+        <v>7014080</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -23783,7 +23776,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 4 st fröställningar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -23803,7 +23796,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -23959,10 +23952,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121339956</v>
+        <v>121339991</v>
       </c>
       <c r="B171" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -23971,61 +23964,44 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>500265</v>
+        <v>500281</v>
       </c>
       <c r="R171" t="n">
-        <v>7013735</v>
+        <v>7013721</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -24059,7 +24035,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -24080,6 +24056,26 @@
       <c r="AI171" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -24097,10 +24093,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121339891</v>
+        <v>121339897</v>
       </c>
       <c r="B172" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -24109,35 +24105,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N172" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24189,7 +24193,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -24198,6 +24202,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -24209,26 +24214,6 @@
       <c r="AI172" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -24246,10 +24231,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121339476</v>
+        <v>121340000</v>
       </c>
       <c r="B173" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -24258,61 +24243,48 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>500200</v>
+        <v>500299</v>
       </c>
       <c r="R173" t="n">
-        <v>7014028</v>
+        <v>7013696</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -24346,7 +24318,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -24366,7 +24338,27 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -24384,10 +24376,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121339782</v>
+        <v>121339891</v>
       </c>
       <c r="B174" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -24396,43 +24388,35 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N174" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24440,14 +24424,14 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>500152</v>
+        <v>500163</v>
       </c>
       <c r="R174" t="n">
-        <v>7013957</v>
+        <v>7013970</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -24484,7 +24468,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Äldre ringhack av tretåig hackspett på en gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -24493,7 +24477,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -24504,7 +24487,27 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -24522,10 +24525,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121335603</v>
+        <v>121338927</v>
       </c>
       <c r="B175" t="n">
-        <v>57356</v>
+        <v>98022</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -24534,35 +24537,43 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N175" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24570,17 +24581,17 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Gammal granskog vid Fjälån-Hansbodarna, Östersjön, Kyrkås, Jmt</t>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>500182</v>
+        <v>500220</v>
       </c>
       <c r="R175" t="n">
-        <v>7014067</v>
+        <v>7014127</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -24614,7 +24625,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -24623,6 +24634,7 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -24633,27 +24645,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -24671,10 +24663,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121339744</v>
+        <v>121338977</v>
       </c>
       <c r="B176" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -24683,56 +24675,61 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>500169</v>
+        <v>500191</v>
       </c>
       <c r="R176" t="n">
-        <v>7013982</v>
+        <v>7014126</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -24766,7 +24763,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -24786,27 +24783,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -24824,10 +24801,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121338977</v>
+        <v>121339923</v>
       </c>
       <c r="B177" t="n">
-        <v>98105</v>
+        <v>91403</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -24836,61 +24813,56 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500191</v>
+        <v>500108</v>
       </c>
       <c r="R177" t="n">
-        <v>7014126</v>
+        <v>7013909</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -24920,11 +24892,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Knärot med minst 11 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -24944,7 +24911,27 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -24962,10 +24949,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121339038</v>
+        <v>121339861</v>
       </c>
       <c r="B178" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -24974,58 +24961,41 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500173</v>
+        <v>500140</v>
       </c>
       <c r="R178" t="n">
-        <v>7014080</v>
+        <v>7013999</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -25062,7 +25032,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Knärot med minst 65 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -25082,7 +25052,32 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall och björk nära ett större vattendrag. Skogen här är bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -25100,10 +25095,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121335375</v>
+        <v>121339542</v>
       </c>
       <c r="B179" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25112,61 +25107,56 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>500170</v>
+        <v>500188</v>
       </c>
       <c r="R179" t="n">
-        <v>7014032</v>
+        <v>7013973</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -25200,7 +25190,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -25220,7 +25210,27 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -25238,10 +25248,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121339991</v>
+        <v>121339956</v>
       </c>
       <c r="B180" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -25250,44 +25260,61 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>500281</v>
+        <v>500265</v>
       </c>
       <c r="R180" t="n">
-        <v>7013721</v>
+        <v>7013735</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -25321,7 +25348,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Resupinata fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 160 st skott/stjälkar och 7 st fröställningar inom ca 1,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -25342,26 +25369,6 @@
       <c r="AI180" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -25379,10 +25386,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121339542</v>
+        <v>121339476</v>
       </c>
       <c r="B181" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -25391,56 +25398,61 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>500188</v>
+        <v>500200</v>
       </c>
       <c r="R181" t="n">
-        <v>7013973</v>
+        <v>7014028</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -25474,7 +25486,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på en granlåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 10 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -25495,26 +25507,6 @@
       <c r="AI181" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med inslag av tall och björk på frisk- och frisk-fuktig mark. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25532,10 +25524,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121339897</v>
+        <v>121335603</v>
       </c>
       <c r="B182" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25544,43 +25536,35 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25592,10 +25576,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>500163</v>
+        <v>500182</v>
       </c>
       <c r="R182" t="n">
-        <v>7013970</v>
+        <v>7014067</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -25632,7 +25616,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 3 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Hackspår längs flera meter på en granstam som bedöms vara skapade inom 5 år bakåt. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25641,7 +25625,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -25652,7 +25635,27 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk-fuktig och fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25670,10 +25673,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121338927</v>
+        <v>121339744</v>
       </c>
       <c r="B183" t="n">
-        <v>98022</v>
+        <v>90738</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25682,61 +25685,56 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>500220</v>
+        <v>500169</v>
       </c>
       <c r="R183" t="n">
-        <v>7014127</v>
+        <v>7013982</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -25790,7 +25788,27 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg intill ett större vattendrag. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder av liggande och stående död ved. På fuktig och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med inslag av högörter. Spår av bäver.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25808,10 +25826,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121339923</v>
+        <v>121335375</v>
       </c>
       <c r="B184" t="n">
-        <v>91403</v>
+        <v>98105</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25820,53 +25838,58 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500108</v>
+        <v>500170</v>
       </c>
       <c r="R184" t="n">
-        <v>7013909</v>
+        <v>7014032</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -25901,6 +25924,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Knärot med minst 50 st skott/stjälkar och 6 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25918,27 +25946,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Stump # En stubbe av en knäckt gran. # Picea abies</t>
+          <t>Grandominerad gammal skog med inslag av tall, björk, rönn och sälg. Skogen här är flerskiktad, bitvis luckig och har olikåldriga träd. Bitvis måttliga mängder med liggande och stående död ved. På frisk- och frisk-fuktig mark. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i luckiga mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25956,10 +25964,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121339861</v>
+        <v>121339782</v>
       </c>
       <c r="B185" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25968,41 +25976,58 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>500140</v>
+        <v>500152</v>
       </c>
       <c r="R185" t="n">
-        <v>7013999</v>
+        <v>7013957</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -26039,7 +26064,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
+          <t>Knärot med minst 20 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 25277-2024.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -26059,32 +26084,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL185" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk och frisk-fuktig mark. Här finns träd med socklar. Bitvis måttliga mängder med liggande och stående död ved. Bottenskikt med mossor och fältskikt med blåbärs- och lingonris och inslag av högörter särskilt i mer fuktiga partier.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY184"/>
+  <dimension ref="A1:AY185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25974,6 +25974,142 @@
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>125807808</v>
+      </c>
+      <c r="B185" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Gammal granskog vid Fjälån-Hansbodarna, Gammal granskog vid Fjälån-Hansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>499982</v>
+      </c>
+      <c r="R185" t="n">
+        <v>7013955</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Observerades i tät, äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -25979,7 +25979,7 @@
         <v>125807808</v>
       </c>
       <c r="B185" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -25979,7 +25979,7 @@
         <v>125807808</v>
       </c>
       <c r="B185" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -25979,7 +25979,7 @@
         <v>125807808</v>
       </c>
       <c r="B185" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 25277-2024 artfynd.xlsx
+++ b/artfynd/A 25277-2024 artfynd.xlsx
@@ -25979,7 +25979,7 @@
         <v>125807808</v>
       </c>
       <c r="B185" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
